--- a/Challan_Pricelist/Challan_PriceList.xlsx
+++ b/Challan_Pricelist/Challan_PriceList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Challan_Pricelist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35FA375-5ED4-4A15-9966-BC8805FB545C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F7BAAF-3E9C-4137-8C2A-5ED6AC9CEC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9142,7 +9142,7 @@
         <v>36750</v>
       </c>
       <c r="G333">
-        <v>9240</v>
+        <v>8820</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">

--- a/Challan_Pricelist/Challan_PriceList.xlsx
+++ b/Challan_Pricelist/Challan_PriceList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Challan_Pricelist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF01E4EE-7FAB-4895-825F-5D1AC419ACBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B006E7D-ACB6-4F29-AC09-A9D1C5FF2FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="86">
   <si>
     <t>SKU</t>
   </si>
@@ -279,6 +279,10 @@
   <si>
     <t>IOC CLEARBLUE-210 L HD</t>
   </si>
+  <si>
+    <t>ECSTAR PETROL 
+0W-16 FE-210 L</t>
+  </si>
 </sst>
 </file>
 
@@ -333,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -342,18 +346,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11933,7 +11933,7 @@
             <v>256.98020338983054</v>
           </cell>
           <cell r="P140">
-            <v>0</v>
+            <v>72</v>
           </cell>
           <cell r="Q140">
             <v>0</v>
@@ -11942,28 +11942,28 @@
             <v>0</v>
           </cell>
           <cell r="S140">
-            <v>0</v>
+            <v>360</v>
           </cell>
           <cell r="T140">
-            <v>1284.9010169491528</v>
+            <v>924.90101694915279</v>
           </cell>
           <cell r="U140">
-            <v>1516.1832000000002</v>
+            <v>1091.3832000000002</v>
           </cell>
           <cell r="V140">
-            <v>303.23664000000002</v>
+            <v>218.27664000000004</v>
           </cell>
           <cell r="W140">
-            <v>6064.7328000000043</v>
+            <v>4365.5328000000036</v>
           </cell>
           <cell r="X140">
-            <v>91.81679999999983</v>
+            <v>516.61679999999978</v>
           </cell>
           <cell r="Y140">
-            <v>367.26719999999955</v>
+            <v>2066.4672000000005</v>
           </cell>
           <cell r="Z140">
-            <v>18.36336</v>
+            <v>103.32335999999998</v>
           </cell>
           <cell r="AA140">
             <v>6</v>
@@ -12016,7 +12016,7 @@
             <v>249.36072881355935</v>
           </cell>
           <cell r="P141">
-            <v>0</v>
+            <v>75</v>
           </cell>
           <cell r="Q141">
             <v>0</v>
@@ -12025,28 +12025,28 @@
             <v>0</v>
           </cell>
           <cell r="S141">
-            <v>0</v>
+            <v>1500</v>
           </cell>
           <cell r="T141">
-            <v>4987.2145762711871</v>
+            <v>3487.2145762711871</v>
           </cell>
           <cell r="U141">
-            <v>5884.9132000000009</v>
+            <v>4114.9132000000009</v>
           </cell>
           <cell r="V141">
-            <v>294.24566000000004</v>
+            <v>205.74566000000004</v>
           </cell>
           <cell r="W141">
-            <v>5884.9132000000054</v>
+            <v>4114.9132000000036</v>
           </cell>
           <cell r="X141">
-            <v>351.08679999999913</v>
+            <v>2121.0867999999991</v>
           </cell>
           <cell r="Y141">
-            <v>351.08679999999936</v>
+            <v>2121.0868000000005</v>
           </cell>
           <cell r="Z141">
-            <v>17.554339999999968</v>
+            <v>106.05433999999997</v>
           </cell>
           <cell r="AA141">
             <v>6</v>
@@ -12348,7 +12348,7 @@
             <v>184.99004237288139</v>
           </cell>
           <cell r="P145">
-            <v>0</v>
+            <v>34</v>
           </cell>
           <cell r="Q145">
             <v>0</v>
@@ -12357,28 +12357,28 @@
             <v>0</v>
           </cell>
           <cell r="S145">
-            <v>0</v>
+            <v>680</v>
           </cell>
           <cell r="T145">
-            <v>3699.8008474576277</v>
+            <v>3019.8008474576277</v>
           </cell>
           <cell r="U145">
-            <v>4365.7650000000003</v>
+            <v>3563.3650000000007</v>
           </cell>
           <cell r="V145">
-            <v>218.28825000000001</v>
+            <v>178.16825000000003</v>
           </cell>
           <cell r="W145">
-            <v>4365.7650000000031</v>
+            <v>3563.365000000003</v>
           </cell>
           <cell r="X145">
-            <v>1109.2349999999997</v>
+            <v>1911.6349999999993</v>
           </cell>
           <cell r="Y145">
-            <v>1109.2350000000004</v>
+            <v>1911.6350000000007</v>
           </cell>
           <cell r="Z145">
-            <v>55.461749999999995</v>
+            <v>95.581749999999971</v>
           </cell>
           <cell r="AA145">
             <v>0</v>
@@ -44931,7 +44931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G352"/>
+  <dimension ref="A1:G353"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.796875" style="1" bestFit="1" customWidth="1"/>
@@ -44972,16 +44972,16 @@
       <c r="C2" s="6">
         <v>8000.0000000000055</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="3">
         <v>6499.6000000000049</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="3">
         <v>60.000000000000043</v>
       </c>
     </row>
@@ -44996,16 +44996,16 @@
       <c r="C3" s="6">
         <v>8000.0000000000055</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="3">
         <v>6422.8000000000056</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="3">
         <v>60.000000000000043</v>
       </c>
     </row>
@@ -45020,16 +45020,16 @@
       <c r="C4" s="6">
         <v>4000.0000000000018</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="3">
         <v>3199.8000000000015</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="3">
         <v>30.000000000000014</v>
       </c>
     </row>
@@ -45044,16 +45044,16 @@
       <c r="C5" s="6">
         <v>7800.0000000000055</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="3">
         <v>6345.4800000000041</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="3">
         <v>60.000000000000043</v>
       </c>
     </row>
@@ -45068,16 +45068,16 @@
       <c r="C6" s="6">
         <v>7964.9999999999982</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="3">
         <v>17.999999999999996</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="3">
         <v>7109.5589999999984</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="3">
         <v>0</v>
       </c>
     </row>
@@ -45092,16 +45092,16 @@
       <c r="C7" s="6">
         <v>8320.0000000000036</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>20.000000000000011</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="3">
         <v>6410.3200000000024</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="3">
         <v>180.00000000000009</v>
       </c>
     </row>
@@ -45116,16 +45116,16 @@
       <c r="C8" s="6">
         <v>7400.0000000000055</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="3">
         <v>5561.1400000000031</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="3">
         <v>380.00000000000028</v>
       </c>
     </row>
@@ -45140,16 +45140,16 @@
       <c r="C9" s="6">
         <v>7280.0000000000045</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="3">
         <v>5454.9520000000048</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="3">
         <v>380.00000000000028</v>
       </c>
     </row>
@@ -45164,16 +45164,16 @@
       <c r="C10" s="6">
         <v>7730.0000000000055</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="3">
         <v>5861.5990000000029</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="3">
         <v>380.00000000000028</v>
       </c>
     </row>
@@ -45188,16 +45188,16 @@
       <c r="C11" s="6">
         <v>8340.0000000000055</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="3">
         <v>6402.4820000000045</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="3">
         <v>280.00000000000023</v>
       </c>
     </row>
@@ -45212,16 +45212,16 @@
       <c r="C12" s="6">
         <v>8080.0000000000055</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="3">
         <v>6286.3120000000044</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="3">
         <v>280.00000000000023</v>
       </c>
     </row>
@@ -45236,16 +45236,16 @@
       <c r="C13" s="6">
         <v>7440.0000000000045</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="3">
         <v>5726.5040000000035</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="3">
         <v>280.00000000000023</v>
       </c>
     </row>
@@ -45260,16 +45260,16 @@
       <c r="C14" s="6">
         <v>3000</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="3">
         <v>8.4</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="3">
         <v>2407.8000000000002</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="3">
         <v>0</v>
       </c>
     </row>
@@ -45284,16 +45284,16 @@
       <c r="C15" s="6">
         <v>4200</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="3">
         <v>10</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="3">
         <v>3694.7400000000002</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="3">
         <v>0</v>
       </c>
     </row>
@@ -45308,16 +45308,16 @@
       <c r="C16" s="6">
         <v>19800.000000000015</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="3">
         <v>15362.820000000012</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="3">
         <v>0</v>
       </c>
     </row>
@@ -45332,16 +45332,16 @@
       <c r="C17" s="6">
         <v>7280</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="3">
         <v>18</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="3">
         <v>5323.7039999999997</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="3">
         <v>432</v>
       </c>
     </row>
@@ -45356,16 +45356,16 @@
       <c r="C18" s="6">
         <v>8060.0000000000055</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="3">
         <v>5768.2100000000046</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="3">
         <v>600.00000000000045</v>
       </c>
     </row>
@@ -45380,16 +45380,16 @@
       <c r="C19" s="6">
         <v>11080</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="3">
         <v>12</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="3">
         <v>7676.1239999999998</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="3">
         <v>540</v>
       </c>
     </row>
@@ -45404,16 +45404,16 @@
       <c r="C20" s="6">
         <v>10304</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="3">
         <v>11.2</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="3">
         <v>7732.1216000000004</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="3">
         <v>0</v>
       </c>
     </row>
@@ -45428,16 +45428,16 @@
       <c r="C21" s="6">
         <v>9250.0000000000055</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="3">
         <v>5229.2750000000033</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="3">
         <v>1450.0000000000007</v>
       </c>
     </row>
@@ -45452,16 +45452,16 @@
       <c r="C22" s="6">
         <v>9212</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="3">
         <v>10</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="3">
         <v>6910.8423999999995</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="3">
         <v>0</v>
       </c>
     </row>
@@ -45476,16 +45476,16 @@
       <c r="C23" s="6">
         <v>9250</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="3">
         <v>10</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="3">
         <v>6409.2749999999996</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="3">
         <v>450</v>
       </c>
     </row>
@@ -45500,16 +45500,16 @@
       <c r="C24" s="6">
         <v>9260</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="3">
         <v>18</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="3">
         <v>6196.5660000000007</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="3">
         <v>792</v>
       </c>
     </row>
@@ -45524,16 +45524,16 @@
       <c r="C25" s="6">
         <v>10180.000000000007</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="3">
         <v>6816.4880000000039</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="3">
         <v>880.00000000000068</v>
       </c>
     </row>
@@ -45548,16 +45548,16 @@
       <c r="C26" s="6">
         <v>10180</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="3">
         <v>20</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="3">
         <v>6934.4879999999994</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="3">
         <v>780</v>
       </c>
     </row>
@@ -45572,16 +45572,16 @@
       <c r="C27" s="6">
         <v>8720</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="3">
         <v>18</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="3">
         <v>5886.9120000000003</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="3">
         <v>702</v>
       </c>
     </row>
@@ -45596,16 +45596,16 @@
       <c r="C28" s="6">
         <v>8720</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="3">
         <v>18</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="3">
         <v>5780.7119999999995</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="3">
         <v>792</v>
       </c>
     </row>
@@ -45620,16 +45620,16 @@
       <c r="C29" s="6">
         <v>10180.000000000007</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="3">
         <v>6816.4880000000039</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="3">
         <v>880.00000000000068</v>
       </c>
     </row>
@@ -45644,16 +45644,16 @@
       <c r="C30" s="6">
         <v>10180</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="3">
         <v>20</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="3">
         <v>6934.4879999999994</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="3">
         <v>780</v>
       </c>
     </row>
@@ -45668,16 +45668,16 @@
       <c r="C31" s="6">
         <v>9260</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="3">
         <v>18</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="3">
         <v>6302.7660000000005</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="3">
         <v>702</v>
       </c>
     </row>
@@ -45692,16 +45692,16 @@
       <c r="C32" s="6">
         <v>10180</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="3">
         <v>20</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="3">
         <v>6934.4879999999994</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32" s="3">
         <v>780</v>
       </c>
     </row>
@@ -45716,16 +45716,16 @@
       <c r="C33" s="6">
         <v>9260</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="3">
         <v>18</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="3">
         <v>6302.7660000000005</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G33" s="3">
         <v>702</v>
       </c>
     </row>
@@ -45740,16 +45740,16 @@
       <c r="C34" s="6">
         <v>6920</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="3">
         <v>18</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="3">
         <v>3999.76</v>
       </c>
-      <c r="G34" s="7">
+      <c r="G34" s="3">
         <v>0</v>
       </c>
     </row>
@@ -45764,16 +45764,16 @@
       <c r="C35" s="6">
         <v>7620.0000000000055</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="3">
         <v>4443.9840000000031</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="3">
         <v>0</v>
       </c>
     </row>
@@ -45788,16 +45788,16 @@
       <c r="C36" s="6">
         <v>7340</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="3">
         <v>12</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36" s="3">
         <v>4890.2180000000008</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G36" s="3">
         <v>600</v>
       </c>
     </row>
@@ -45812,16 +45812,16 @@
       <c r="C37" s="6">
         <v>7560</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="3">
         <v>16</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37" s="3">
         <v>4724.9439999999995</v>
       </c>
-      <c r="G37" s="7">
+      <c r="G37" s="3">
         <v>560</v>
       </c>
     </row>
@@ -45836,16 +45836,16 @@
       <c r="C38" s="6">
         <v>3200</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="3">
         <v>9</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="3">
         <v>2500.16</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38" s="3">
         <v>0</v>
       </c>
     </row>
@@ -45860,16 +45860,16 @@
       <c r="C39" s="6">
         <v>3500.0000000000018</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="3">
         <v>2749.9500000000007</v>
       </c>
-      <c r="G39" s="7">
+      <c r="G39" s="3">
         <v>0</v>
       </c>
     </row>
@@ -45884,16 +45884,16 @@
       <c r="C40" s="6">
         <v>7560.0000000000009</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="3">
         <v>12.000000000000002</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40" s="3">
         <v>4712.1480000000001</v>
       </c>
-      <c r="G40" s="7">
+      <c r="G40" s="3">
         <v>0</v>
       </c>
     </row>
@@ -45908,16 +45908,16 @@
       <c r="C41" s="6">
         <v>6060</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="3">
         <v>12</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41" s="3">
         <v>4373.5020000000004</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41" s="3">
         <v>0</v>
       </c>
     </row>
@@ -45932,16 +45932,16 @@
       <c r="C42" s="6">
         <v>5160</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="3">
         <v>12</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="3">
         <v>4164.6359999999995</v>
       </c>
-      <c r="G42" s="7">
+      <c r="G42" s="3">
         <v>0</v>
       </c>
     </row>
@@ -45956,16 +45956,16 @@
       <c r="C43" s="6">
         <v>2350</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="3">
         <v>5</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F43" s="3">
         <v>1721.1399999999999</v>
       </c>
-      <c r="G43" s="7">
+      <c r="G43" s="3">
         <v>0</v>
       </c>
     </row>
@@ -45980,16 +45980,16 @@
       <c r="C44" s="6">
         <v>3920.0000000000023</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="3">
         <v>3161.4800000000018</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G44" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46004,16 +46004,16 @@
       <c r="C45" s="6">
         <v>7440.0000000000055</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45" s="3">
         <v>6186.3600000000051</v>
       </c>
-      <c r="G45" s="7">
+      <c r="G45" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46028,16 +46028,16 @@
       <c r="C46" s="6">
         <v>2430</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D46" s="3">
         <v>5</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F46" s="3">
         <v>1995.0299999999997</v>
       </c>
-      <c r="G46" s="7">
+      <c r="G46" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46052,16 +46052,16 @@
       <c r="C47" s="6">
         <v>4700.0000000000027</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E47" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F47" s="7">
+      <c r="F47" s="3">
         <v>3873.2700000000023</v>
       </c>
-      <c r="G47" s="7">
+      <c r="G47" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46076,16 +46076,16 @@
       <c r="C48" s="6">
         <v>3410</v>
       </c>
-      <c r="D48" s="7">
+      <c r="D48" s="3">
         <v>5</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F48" s="3">
         <v>2493.0509999999999</v>
       </c>
-      <c r="G48" s="7">
+      <c r="G48" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46100,16 +46100,16 @@
       <c r="C49" s="6">
         <v>6500.0000000000036</v>
       </c>
-      <c r="D49" s="7">
+      <c r="D49" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F49" s="3">
         <v>4797.6500000000024</v>
       </c>
-      <c r="G49" s="7">
+      <c r="G49" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46124,16 +46124,16 @@
       <c r="C50" s="6">
         <v>3220.0000000000018</v>
       </c>
-      <c r="D50" s="7">
+      <c r="D50" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E50" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F50" s="7">
+      <c r="F50" s="3">
         <v>2774.6740000000013</v>
       </c>
-      <c r="G50" s="7">
+      <c r="G50" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46148,16 +46148,16 @@
       <c r="C51" s="6">
         <v>7160</v>
       </c>
-      <c r="D51" s="7">
+      <c r="D51" s="3">
         <v>18</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E51" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F51" s="7">
+      <c r="F51" s="3">
         <v>4951.6359999999995</v>
       </c>
-      <c r="G51" s="7">
+      <c r="G51" s="3">
         <v>252</v>
       </c>
     </row>
@@ -46172,16 +46172,16 @@
       <c r="C52" s="6">
         <v>8500.0000000000055</v>
       </c>
-      <c r="D52" s="7">
+      <c r="D52" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E52" s="7" t="s">
+      <c r="E52" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F52" s="7">
+      <c r="F52" s="3">
         <v>5940.9000000000042</v>
       </c>
-      <c r="G52" s="7">
+      <c r="G52" s="3">
         <v>280.00000000000023</v>
       </c>
     </row>
@@ -46196,16 +46196,16 @@
       <c r="C53" s="6">
         <v>8500</v>
       </c>
-      <c r="D53" s="7">
+      <c r="D53" s="3">
         <v>20</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E53" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F53" s="7">
+      <c r="F53" s="3">
         <v>6200.5000000000009</v>
       </c>
-      <c r="G53" s="7">
+      <c r="G53" s="3">
         <v>60</v>
       </c>
     </row>
@@ -46220,16 +46220,16 @@
       <c r="C54" s="6">
         <v>7700</v>
       </c>
-      <c r="D54" s="7">
+      <c r="D54" s="3">
         <v>18</v>
       </c>
-      <c r="E54" s="7" t="s">
+      <c r="E54" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F54" s="7">
+      <c r="F54" s="3">
         <v>5581.1500000000015</v>
       </c>
-      <c r="G54" s="7">
+      <c r="G54" s="3">
         <v>54</v>
       </c>
     </row>
@@ -46244,16 +46244,16 @@
       <c r="C55" s="6">
         <v>6840</v>
       </c>
-      <c r="D55" s="7">
+      <c r="D55" s="3">
         <v>18</v>
       </c>
-      <c r="E55" s="7" t="s">
+      <c r="E55" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F55" s="7">
+      <c r="F55" s="3">
         <v>4994.5319999999992</v>
       </c>
-      <c r="G55" s="7">
+      <c r="G55" s="3">
         <v>360</v>
       </c>
     </row>
@@ -46268,16 +46268,16 @@
       <c r="C56" s="6">
         <v>7600.0000000000055</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D56" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E56" s="7" t="s">
+      <c r="E56" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F56" s="7">
+      <c r="F56" s="3">
         <v>5549.4800000000041</v>
       </c>
-      <c r="G56" s="7">
+      <c r="G56" s="3">
         <v>400.00000000000028</v>
       </c>
     </row>
@@ -46292,16 +46292,16 @@
       <c r="C57" s="6">
         <v>9600.0000000000073</v>
       </c>
-      <c r="D57" s="7">
+      <c r="D57" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E57" s="7" t="s">
+      <c r="E57" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F57" s="7">
+      <c r="F57" s="3">
         <v>6232.0800000000045</v>
       </c>
-      <c r="G57" s="7">
+      <c r="G57" s="3">
         <v>180.00000000000011</v>
       </c>
     </row>
@@ -46316,16 +46316,16 @@
       <c r="C58" s="6">
         <v>11440</v>
       </c>
-      <c r="D58" s="7">
+      <c r="D58" s="3">
         <v>24</v>
       </c>
-      <c r="E58" s="7" t="s">
+      <c r="E58" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F58" s="7">
+      <c r="F58" s="3">
         <v>7462.5439999999981</v>
       </c>
-      <c r="G58" s="7">
+      <c r="G58" s="3">
         <v>216</v>
       </c>
     </row>
@@ -46340,16 +46340,16 @@
       <c r="C59" s="6">
         <v>9600</v>
       </c>
-      <c r="D59" s="7">
+      <c r="D59" s="3">
         <v>20</v>
       </c>
-      <c r="E59" s="7" t="s">
+      <c r="E59" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F59" s="7">
+      <c r="F59" s="3">
         <v>6232.08</v>
       </c>
-      <c r="G59" s="7">
+      <c r="G59" s="3">
         <v>180</v>
       </c>
     </row>
@@ -46364,16 +46364,16 @@
       <c r="C60" s="6">
         <v>6480</v>
       </c>
-      <c r="D60" s="7">
+      <c r="D60" s="3">
         <v>16</v>
       </c>
-      <c r="E60" s="7" t="s">
+      <c r="E60" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F60" s="7">
+      <c r="F60" s="3">
         <v>4554.768</v>
       </c>
-      <c r="G60" s="7">
+      <c r="G60" s="3">
         <v>240</v>
       </c>
     </row>
@@ -46388,16 +46388,16 @@
       <c r="C61" s="6">
         <v>7900</v>
       </c>
-      <c r="D61" s="7">
+      <c r="D61" s="3">
         <v>18</v>
       </c>
-      <c r="E61" s="7" t="s">
+      <c r="E61" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F61" s="7">
+      <c r="F61" s="3">
         <v>5409.6</v>
       </c>
-      <c r="G61" s="7">
+      <c r="G61" s="3">
         <v>252</v>
       </c>
     </row>
@@ -46412,16 +46412,16 @@
       <c r="C62" s="6">
         <v>8740</v>
       </c>
-      <c r="D62" s="7">
+      <c r="D62" s="3">
         <v>20</v>
       </c>
-      <c r="E62" s="7" t="s">
+      <c r="E62" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F62" s="7">
+      <c r="F62" s="3">
         <v>5999.1080000000002</v>
       </c>
-      <c r="G62" s="7">
+      <c r="G62" s="3">
         <v>280</v>
       </c>
     </row>
@@ -46436,16 +46436,16 @@
       <c r="C63" s="6">
         <v>7900</v>
       </c>
-      <c r="D63" s="7">
+      <c r="D63" s="3">
         <v>18</v>
       </c>
-      <c r="E63" s="7" t="s">
+      <c r="E63" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F63" s="7">
+      <c r="F63" s="3">
         <v>5409.6</v>
       </c>
-      <c r="G63" s="7">
+      <c r="G63" s="3">
         <v>252</v>
       </c>
     </row>
@@ -46460,16 +46460,16 @@
       <c r="C64" s="6">
         <v>8520</v>
       </c>
-      <c r="D64" s="7">
+      <c r="D64" s="3">
         <v>20</v>
       </c>
-      <c r="E64" s="7" t="s">
+      <c r="E64" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F64" s="7">
+      <c r="F64" s="3">
         <v>6594.4840000000004</v>
       </c>
-      <c r="G64" s="7">
+      <c r="G64" s="3">
         <v>200</v>
       </c>
     </row>
@@ -46484,16 +46484,16 @@
       <c r="C65" s="6">
         <v>7800</v>
       </c>
-      <c r="D65" s="7">
+      <c r="D65" s="3">
         <v>18</v>
       </c>
-      <c r="E65" s="7" t="s">
+      <c r="E65" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F65" s="7">
+      <c r="F65" s="3">
         <v>5939.46</v>
       </c>
-      <c r="G65" s="7">
+      <c r="G65" s="3">
         <v>180</v>
       </c>
     </row>
@@ -46508,16 +46508,16 @@
       <c r="C66" s="6">
         <v>12900.000000000009</v>
       </c>
-      <c r="D66" s="7">
+      <c r="D66" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E66" s="7" t="s">
+      <c r="E66" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F66" s="7">
+      <c r="F66" s="3">
         <v>8704.4500000000062</v>
       </c>
-      <c r="G66" s="7">
+      <c r="G66" s="3">
         <v>500.00000000000034</v>
       </c>
     </row>
@@ -46532,16 +46532,16 @@
       <c r="C67" s="6">
         <v>13020.000000000004</v>
       </c>
-      <c r="D67" s="7">
+      <c r="D67" s="3">
         <v>14.000000000000004</v>
       </c>
-      <c r="E67" s="7" t="s">
+      <c r="E67" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F67" s="7">
+      <c r="F67" s="3">
         <v>10219.398000000001</v>
       </c>
-      <c r="G67" s="7">
+      <c r="G67" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46556,16 +46556,16 @@
       <c r="C68" s="6">
         <v>24200.000000000018</v>
       </c>
-      <c r="D68" s="7">
+      <c r="D68" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E68" s="7" t="s">
+      <c r="E68" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F68" s="7">
+      <c r="F68" s="3">
         <v>16095.420000000015</v>
       </c>
-      <c r="G68" s="7">
+      <c r="G68" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46580,16 +46580,16 @@
       <c r="C69" s="6">
         <v>19360.000000000015</v>
       </c>
-      <c r="D69" s="7">
+      <c r="D69" s="3">
         <v>16.000000000000011</v>
       </c>
-      <c r="E69" s="7" t="s">
+      <c r="E69" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F69" s="7">
+      <c r="F69" s="3">
         <v>12876.336000000012</v>
       </c>
-      <c r="G69" s="7">
+      <c r="G69" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46604,16 +46604,16 @@
       <c r="C70" s="6">
         <v>8652</v>
       </c>
-      <c r="D70" s="7">
+      <c r="D70" s="3">
         <v>14</v>
       </c>
-      <c r="E70" s="7" t="s">
+      <c r="E70" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F70" s="7">
+      <c r="F70" s="3">
         <v>5221.7759999999998</v>
       </c>
-      <c r="G70" s="7">
+      <c r="G70" s="3">
         <v>546</v>
       </c>
     </row>
@@ -46628,16 +46628,16 @@
       <c r="C71" s="6">
         <v>12640.000000000009</v>
       </c>
-      <c r="D71" s="7">
+      <c r="D71" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E71" s="7" t="s">
+      <c r="E71" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F71" s="7">
+      <c r="F71" s="3">
         <v>7773.8400000000047</v>
       </c>
-      <c r="G71" s="7">
+      <c r="G71" s="3">
         <v>680.00000000000045</v>
       </c>
     </row>
@@ -46652,16 +46652,16 @@
       <c r="C72" s="6">
         <v>7424</v>
       </c>
-      <c r="D72" s="7">
+      <c r="D72" s="3">
         <v>12</v>
       </c>
-      <c r="E72" s="7" t="s">
+      <c r="E72" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F72" s="7">
+      <c r="F72" s="3">
         <v>4484.2015999999994</v>
       </c>
-      <c r="G72" s="7">
+      <c r="G72" s="3">
         <v>468</v>
       </c>
     </row>
@@ -46676,16 +46676,16 @@
       <c r="C73" s="6">
         <v>8652.0000000000018</v>
       </c>
-      <c r="D73" s="7">
+      <c r="D73" s="3">
         <v>14.000000000000004</v>
       </c>
-      <c r="E73" s="7" t="s">
+      <c r="E73" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F73" s="7">
+      <c r="F73" s="3">
         <v>5056.5760000000009</v>
       </c>
-      <c r="G73" s="7">
+      <c r="G73" s="3">
         <v>686.00000000000023</v>
       </c>
     </row>
@@ -46700,16 +46700,16 @@
       <c r="C74" s="6">
         <v>6008.0000000000009</v>
       </c>
-      <c r="D74" s="7">
+      <c r="D74" s="3">
         <v>14.000000000000004</v>
       </c>
-      <c r="E74" s="7" t="s">
+      <c r="E74" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F74" s="7">
+      <c r="F74" s="3">
         <v>4439.0408000000007</v>
       </c>
-      <c r="G74" s="7">
+      <c r="G74" s="3">
         <v>210.00000000000006</v>
       </c>
     </row>
@@ -46724,16 +46724,16 @@
       <c r="C75" s="6">
         <v>4724</v>
       </c>
-      <c r="D75" s="7">
+      <c r="D75" s="3">
         <v>10</v>
       </c>
-      <c r="E75" s="7" t="s">
+      <c r="E75" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F75" s="7">
+      <c r="F75" s="3">
         <v>3121.0744</v>
       </c>
-      <c r="G75" s="7">
+      <c r="G75" s="3">
         <v>400</v>
       </c>
     </row>
@@ -46748,16 +46748,16 @@
       <c r="C76" s="6">
         <v>11840</v>
       </c>
-      <c r="D76" s="7">
+      <c r="D76" s="3">
         <v>24</v>
       </c>
-      <c r="E76" s="7" t="s">
+      <c r="E76" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F76" s="7">
+      <c r="F76" s="3">
         <v>7698.655999999999</v>
       </c>
-      <c r="G76" s="7">
+      <c r="G76" s="3">
         <v>960</v>
       </c>
     </row>
@@ -46772,16 +46772,16 @@
       <c r="C77" s="6">
         <v>12000.000000000009</v>
       </c>
-      <c r="D77" s="7">
+      <c r="D77" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E77" s="7" t="s">
+      <c r="E77" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F77" s="7">
+      <c r="F77" s="3">
         <v>11400.000000000007</v>
       </c>
-      <c r="G77" s="7">
+      <c r="G77" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46796,16 +46796,16 @@
       <c r="C78" s="6">
         <v>5910.0000000000036</v>
       </c>
-      <c r="D78" s="7">
+      <c r="D78" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E78" s="7" t="s">
+      <c r="E78" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F78" s="7">
+      <c r="F78" s="3">
         <v>5582.586000000003</v>
       </c>
-      <c r="G78" s="7">
+      <c r="G78" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46820,16 +46820,16 @@
       <c r="C79" s="6">
         <v>5982.0000000000036</v>
       </c>
-      <c r="D79" s="7">
+      <c r="D79" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E79" s="7" t="s">
+      <c r="E79" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F79" s="7">
+      <c r="F79" s="3">
         <v>5649.4008000000022</v>
       </c>
-      <c r="G79" s="7">
+      <c r="G79" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46844,16 +46844,16 @@
       <c r="C80" s="6">
         <v>6432.0000000000045</v>
       </c>
-      <c r="D80" s="7">
+      <c r="D80" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E80" s="7" t="s">
+      <c r="E80" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F80" s="7">
+      <c r="F80" s="3">
         <v>6064.7328000000043</v>
       </c>
-      <c r="G80" s="7">
+      <c r="G80" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46868,16 +46868,16 @@
       <c r="C81" s="6">
         <v>6236.0000000000045</v>
       </c>
-      <c r="D81" s="7">
+      <c r="D81" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E81" s="7" t="s">
+      <c r="E81" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F81" s="7">
+      <c r="F81" s="3">
         <v>5884.9132000000045</v>
       </c>
-      <c r="G81" s="7">
+      <c r="G81" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46892,16 +46892,16 @@
       <c r="C82" s="6">
         <v>6053.0000000000036</v>
       </c>
-      <c r="D82" s="7">
+      <c r="D82" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E82" s="7" t="s">
+      <c r="E82" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F82" s="7">
+      <c r="F82" s="3">
         <v>5714.6373000000031</v>
       </c>
-      <c r="G82" s="7">
+      <c r="G82" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46916,16 +46916,16 @@
       <c r="C83" s="6">
         <v>5475.0000000000036</v>
       </c>
-      <c r="D83" s="7">
+      <c r="D83" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E83" s="7" t="s">
+      <c r="E83" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F83" s="7">
+      <c r="F83" s="3">
         <v>4365.7650000000031</v>
       </c>
-      <c r="G83" s="7">
+      <c r="G83" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46940,16 +46940,16 @@
       <c r="C84" s="6">
         <v>6704.0000000000045</v>
       </c>
-      <c r="D84" s="7">
+      <c r="D84" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E84" s="7" t="s">
+      <c r="E84" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F84" s="7">
+      <c r="F84" s="3">
         <v>5587.1136000000033</v>
       </c>
-      <c r="G84" s="7">
+      <c r="G84" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46964,16 +46964,16 @@
       <c r="C85" s="6">
         <v>7303.0000000000045</v>
       </c>
-      <c r="D85" s="7">
+      <c r="D85" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E85" s="7" t="s">
+      <c r="E85" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F85" s="7">
+      <c r="F85" s="3">
         <v>6085.5899000000036</v>
       </c>
-      <c r="G85" s="7">
+      <c r="G85" s="3">
         <v>0</v>
       </c>
     </row>
@@ -46988,16 +46988,16 @@
       <c r="C86" s="6">
         <v>7300.0000000000045</v>
       </c>
-      <c r="D86" s="7">
+      <c r="D86" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E86" s="7" t="s">
+      <c r="E86" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F86" s="7">
+      <c r="F86" s="3">
         <v>6515.9800000000041</v>
       </c>
-      <c r="G86" s="7">
+      <c r="G86" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47012,16 +47012,16 @@
       <c r="C87" s="6">
         <v>6792.0000000000045</v>
       </c>
-      <c r="D87" s="7">
+      <c r="D87" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E87" s="7" t="s">
+      <c r="E87" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F87" s="7">
+      <c r="F87" s="3">
         <v>6399.422400000004</v>
       </c>
-      <c r="G87" s="7">
+      <c r="G87" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47036,16 +47036,16 @@
       <c r="C88" s="6">
         <v>7500.0000000000055</v>
       </c>
-      <c r="D88" s="7">
+      <c r="D88" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E88" s="7" t="s">
+      <c r="E88" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F88" s="7">
+      <c r="F88" s="3">
         <v>6694.5000000000064</v>
       </c>
-      <c r="G88" s="7">
+      <c r="G88" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47060,16 +47060,16 @@
       <c r="C89" s="6">
         <v>6378.0000000000045</v>
       </c>
-      <c r="D89" s="7">
+      <c r="D89" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E89" s="7" t="s">
+      <c r="E89" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F89" s="7">
+      <c r="F89" s="3">
         <v>6016.3674000000037</v>
       </c>
-      <c r="G89" s="7">
+      <c r="G89" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47084,16 +47084,16 @@
       <c r="C90" s="6">
         <v>6585.0000000000045</v>
       </c>
-      <c r="D90" s="7">
+      <c r="D90" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E90" s="7" t="s">
+      <c r="E90" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F90" s="7">
+      <c r="F90" s="3">
         <v>6208.3380000000052</v>
       </c>
-      <c r="G90" s="7">
+      <c r="G90" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47108,16 +47108,16 @@
       <c r="C91" s="6">
         <v>6383.0000000000045</v>
       </c>
-      <c r="D91" s="7">
+      <c r="D91" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E91" s="7" t="s">
+      <c r="E91" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F91" s="7">
+      <c r="F91" s="3">
         <v>6021.0839000000042</v>
       </c>
-      <c r="G91" s="7">
+      <c r="G91" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47132,16 +47132,16 @@
       <c r="C92" s="6">
         <v>4704.0000000000009</v>
       </c>
-      <c r="D92" s="7">
+      <c r="D92" s="3">
         <v>14.000000000000004</v>
       </c>
-      <c r="E92" s="7" t="s">
+      <c r="E92" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F92" s="7">
+      <c r="F92" s="3">
         <v>3541.7424000000005</v>
       </c>
-      <c r="G92" s="7">
+      <c r="G92" s="3">
         <v>210.00000000000006</v>
       </c>
     </row>
@@ -47156,16 +47156,16 @@
       <c r="C93" s="6">
         <v>4484.0000000000009</v>
       </c>
-      <c r="D93" s="7">
+      <c r="D93" s="3">
         <v>14.000000000000004</v>
       </c>
-      <c r="E93" s="7" t="s">
+      <c r="E93" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F93" s="7">
+      <c r="F93" s="3">
         <v>3315.0212000000015</v>
       </c>
-      <c r="G93" s="7">
+      <c r="G93" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47180,16 +47180,16 @@
       <c r="C94" s="6">
         <v>6098.0000000000036</v>
       </c>
-      <c r="D94" s="7">
+      <c r="D94" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E94" s="7" t="s">
+      <c r="E94" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F94" s="7">
+      <c r="F94" s="3">
         <v>5669.3106000000034</v>
       </c>
-      <c r="G94" s="7">
+      <c r="G94" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47204,16 +47204,16 @@
       <c r="C95" s="6">
         <v>4420.0000000000027</v>
       </c>
-      <c r="D95" s="7">
+      <c r="D95" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E95" s="7" t="s">
+      <c r="E95" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F95" s="7">
+      <c r="F95" s="3">
         <v>3336.5380000000018</v>
       </c>
-      <c r="G95" s="7">
+      <c r="G95" s="3">
         <v>90.000000000000043</v>
       </c>
     </row>
@@ -47228,16 +47228,16 @@
       <c r="C96" s="6">
         <v>8400.0000000000055</v>
       </c>
-      <c r="D96" s="7">
+      <c r="D96" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E96" s="7" t="s">
+      <c r="E96" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F96" s="7">
+      <c r="F96" s="3">
         <v>6439.560000000004</v>
       </c>
-      <c r="G96" s="7">
+      <c r="G96" s="3">
         <v>180.00000000000011</v>
       </c>
     </row>
@@ -47252,16 +47252,16 @@
       <c r="C97" s="6">
         <v>8000.0000000000055</v>
       </c>
-      <c r="D97" s="7">
+      <c r="D97" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E97" s="7" t="s">
+      <c r="E97" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F97" s="7">
+      <c r="F97" s="3">
         <v>6299.600000000004</v>
       </c>
-      <c r="G97" s="7">
+      <c r="G97" s="3">
         <v>180.00000000000011</v>
       </c>
     </row>
@@ -47276,16 +47276,16 @@
       <c r="C98" s="6">
         <v>4400.0000000000018</v>
       </c>
-      <c r="D98" s="7">
+      <c r="D98" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E98" s="7" t="s">
+      <c r="E98" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F98" s="7">
+      <c r="F98" s="3">
         <v>3927.4400000000019</v>
       </c>
-      <c r="G98" s="7">
+      <c r="G98" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47300,16 +47300,16 @@
       <c r="C99" s="6">
         <v>5985.0000000000036</v>
       </c>
-      <c r="D99" s="7">
+      <c r="D99" s="3">
         <v>15.000000000000009</v>
       </c>
-      <c r="E99" s="7" t="s">
+      <c r="E99" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F99" s="7">
+      <c r="F99" s="3">
         <v>5342.211000000003</v>
       </c>
-      <c r="G99" s="7">
+      <c r="G99" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47324,16 +47324,16 @@
       <c r="C100" s="6">
         <v>7000.0000000000045</v>
       </c>
-      <c r="D100" s="7">
+      <c r="D100" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E100" s="7" t="s">
+      <c r="E100" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F100" s="7">
+      <c r="F100" s="3">
         <v>5933.2000000000044</v>
       </c>
-      <c r="G100" s="7">
+      <c r="G100" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47348,16 +47348,16 @@
       <c r="C101" s="6">
         <v>7700.0000000000055</v>
       </c>
-      <c r="D101" s="7">
+      <c r="D101" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E101" s="7" t="s">
+      <c r="E101" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F101" s="7">
+      <c r="F101" s="3">
         <v>5641.6100000000042</v>
       </c>
-      <c r="G101" s="7">
+      <c r="G101" s="3">
         <v>500.00000000000034</v>
       </c>
     </row>
@@ -47372,16 +47372,16 @@
       <c r="C102" s="6">
         <v>7600.0000000000055</v>
       </c>
-      <c r="D102" s="7">
+      <c r="D102" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E102" s="7" t="s">
+      <c r="E102" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F102" s="7">
+      <c r="F102" s="3">
         <v>5217.3600000000042</v>
       </c>
-      <c r="G102" s="7">
+      <c r="G102" s="3">
         <v>780.00000000000057</v>
       </c>
     </row>
@@ -47396,16 +47396,16 @@
       <c r="C103" s="6">
         <v>6620</v>
       </c>
-      <c r="D103" s="7">
+      <c r="D103" s="3">
         <v>20</v>
       </c>
-      <c r="E103" s="7" t="s">
+      <c r="E103" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F103" s="7">
+      <c r="F103" s="3">
         <v>4647.1839999999984</v>
       </c>
-      <c r="G103" s="7">
+      <c r="G103" s="3">
         <v>680</v>
       </c>
     </row>
@@ -47420,16 +47420,16 @@
       <c r="C104" s="6">
         <v>6500.0000000000045</v>
       </c>
-      <c r="D104" s="7">
+      <c r="D104" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E104" s="7" t="s">
+      <c r="E104" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F104" s="7">
+      <c r="F104" s="3">
         <v>4445.3500000000031</v>
       </c>
-      <c r="G104" s="7">
+      <c r="G104" s="3">
         <v>260.00000000000017</v>
       </c>
     </row>
@@ -47444,16 +47444,16 @@
       <c r="C105" s="6">
         <v>4160.0000000000018</v>
       </c>
-      <c r="D105" s="7">
+      <c r="D105" s="3">
         <v>12.000000000000005</v>
       </c>
-      <c r="E105" s="7" t="s">
+      <c r="E105" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F105" s="7">
+      <c r="F105" s="3">
         <v>2900.1440000000011</v>
       </c>
-      <c r="G105" s="7">
+      <c r="G105" s="3">
         <v>156.00000000000006</v>
       </c>
     </row>
@@ -47468,16 +47468,16 @@
       <c r="C106" s="6">
         <v>7100</v>
       </c>
-      <c r="D106" s="7">
+      <c r="D106" s="3">
         <v>20</v>
       </c>
-      <c r="E106" s="7" t="s">
+      <c r="E106" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F106" s="7">
+      <c r="F106" s="3">
         <v>4884.01</v>
       </c>
-      <c r="G106" s="7">
+      <c r="G106" s="3">
         <v>260</v>
       </c>
     </row>
@@ -47492,16 +47492,16 @@
       <c r="C107" s="6">
         <v>5900.0000000000045</v>
       </c>
-      <c r="D107" s="7">
+      <c r="D107" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E107" s="7" t="s">
+      <c r="E107" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F107" s="7">
+      <c r="F107" s="3">
         <v>3443.8300000000022</v>
       </c>
-      <c r="G107" s="7">
+      <c r="G107" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47516,16 +47516,16 @@
       <c r="C108" s="6">
         <v>5400.0000000000036</v>
       </c>
-      <c r="D108" s="7">
+      <c r="D108" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E108" s="7" t="s">
+      <c r="E108" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F108" s="7">
+      <c r="F108" s="3">
         <v>2968.9200000000019</v>
       </c>
-      <c r="G108" s="7">
+      <c r="G108" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47540,16 +47540,16 @@
       <c r="C109" s="6">
         <v>7840.0000000000055</v>
       </c>
-      <c r="D109" s="7">
+      <c r="D109" s="3">
         <v>16.000000000000011</v>
       </c>
-      <c r="E109" s="7" t="s">
+      <c r="E109" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F109" s="7">
+      <c r="F109" s="3">
         <v>6464.0800000000045</v>
       </c>
-      <c r="G109" s="7">
+      <c r="G109" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47564,16 +47564,16 @@
       <c r="C110" s="6">
         <v>15540.000000000004</v>
       </c>
-      <c r="D110" s="7">
+      <c r="D110" s="3">
         <v>14.000000000000004</v>
       </c>
-      <c r="E110" s="7" t="s">
+      <c r="E110" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F110" s="7">
+      <c r="F110" s="3">
         <v>12523.686000000005</v>
       </c>
-      <c r="G110" s="7">
+      <c r="G110" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47588,16 +47588,16 @@
       <c r="C111" s="6">
         <v>7144.0000000000018</v>
       </c>
-      <c r="D111" s="7">
+      <c r="D111" s="3">
         <v>14.000000000000004</v>
       </c>
-      <c r="E111" s="7" t="s">
+      <c r="E111" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F111" s="7">
+      <c r="F111" s="3">
         <v>4874.4680000000008</v>
       </c>
-      <c r="G111" s="7">
+      <c r="G111" s="3">
         <v>770.00000000000023</v>
       </c>
     </row>
@@ -47612,16 +47612,16 @@
       <c r="C112" s="6">
         <v>7380.0000000000055</v>
       </c>
-      <c r="D112" s="7">
+      <c r="D112" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E112" s="7" t="s">
+      <c r="E112" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F112" s="7">
+      <c r="F112" s="3">
         <v>5065.5500000000047</v>
       </c>
-      <c r="G112" s="7">
+      <c r="G112" s="3">
         <v>820.00000000000057</v>
       </c>
     </row>
@@ -47636,16 +47636,16 @@
       <c r="C113" s="6">
         <v>2629.0000000000018</v>
       </c>
-      <c r="D113" s="7">
+      <c r="D113" s="3">
         <v>7.5000000000000053</v>
       </c>
-      <c r="E113" s="7" t="s">
+      <c r="E113" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F113" s="7">
+      <c r="F113" s="3">
         <v>1921.9137000000012</v>
       </c>
-      <c r="G113" s="7">
+      <c r="G113" s="3">
         <v>210.00000000000014</v>
       </c>
     </row>
@@ -47660,16 +47660,16 @@
       <c r="C114" s="6">
         <v>3411.0000000000023</v>
       </c>
-      <c r="D114" s="7">
+      <c r="D114" s="3">
         <v>7.5000000000000053</v>
       </c>
-      <c r="E114" s="7" t="s">
+      <c r="E114" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F114" s="7">
+      <c r="F114" s="3">
         <v>2288.8242000000009</v>
       </c>
-      <c r="G114" s="7">
+      <c r="G114" s="3">
         <v>292.50000000000023</v>
       </c>
     </row>
@@ -47684,16 +47684,16 @@
       <c r="C115" s="6">
         <v>3851</v>
       </c>
-      <c r="D115" s="7">
+      <c r="D115" s="3">
         <v>8.5</v>
       </c>
-      <c r="E115" s="7" t="s">
+      <c r="E115" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F115" s="7">
+      <c r="F115" s="3">
         <v>2424.4028000000003</v>
       </c>
-      <c r="G115" s="7">
+      <c r="G115" s="3">
         <v>467.5</v>
       </c>
     </row>
@@ -47708,16 +47708,16 @@
       <c r="C116" s="6">
         <v>6300.0000000000045</v>
       </c>
-      <c r="D116" s="7">
+      <c r="D116" s="3">
         <v>15.000000000000009</v>
       </c>
-      <c r="E116" s="7" t="s">
+      <c r="E116" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F116" s="7">
+      <c r="F116" s="3">
         <v>4415.4900000000034</v>
       </c>
-      <c r="G116" s="7">
+      <c r="G116" s="3">
         <v>675.00000000000045</v>
       </c>
     </row>
@@ -47732,16 +47732,16 @@
       <c r="C117" s="6">
         <v>6020.0000000000045</v>
       </c>
-      <c r="D117" s="7">
+      <c r="D117" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E117" s="7" t="s">
+      <c r="E117" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F117" s="7">
+      <c r="F117" s="3">
         <v>5139.8760000000029</v>
       </c>
-      <c r="G117" s="7">
+      <c r="G117" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47756,16 +47756,16 @@
       <c r="C118" s="6">
         <v>7040.0000000000045</v>
       </c>
-      <c r="D118" s="7">
+      <c r="D118" s="3">
         <v>16.000000000000011</v>
       </c>
-      <c r="E118" s="7" t="s">
+      <c r="E118" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F118" s="7">
+      <c r="F118" s="3">
         <v>5943.8720000000039</v>
       </c>
-      <c r="G118" s="7">
+      <c r="G118" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47780,16 +47780,16 @@
       <c r="C119" s="6">
         <v>12860.000000000009</v>
       </c>
-      <c r="D119" s="7">
+      <c r="D119" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E119" s="7" t="s">
+      <c r="E119" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F119" s="7">
+      <c r="F119" s="3">
         <v>10771.536000000007</v>
       </c>
-      <c r="G119" s="7">
+      <c r="G119" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47804,16 +47804,16 @@
       <c r="C120" s="6">
         <v>20100.000000000015</v>
       </c>
-      <c r="D120" s="7">
+      <c r="D120" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E120" s="7" t="s">
+      <c r="E120" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F120" s="7">
+      <c r="F120" s="3">
         <v>16520.19000000001</v>
       </c>
-      <c r="G120" s="7">
+      <c r="G120" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47828,16 +47828,16 @@
       <c r="C121" s="6">
         <v>10712</v>
       </c>
-      <c r="D121" s="7">
+      <c r="D121" s="3">
         <v>14</v>
       </c>
-      <c r="E121" s="7" t="s">
+      <c r="E121" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F121" s="7">
+      <c r="F121" s="3">
         <v>6844.6095999999998</v>
       </c>
-      <c r="G121" s="7">
+      <c r="G121" s="3">
         <v>1106</v>
       </c>
     </row>
@@ -47852,16 +47852,16 @@
       <c r="C122" s="6">
         <v>10712.000000000002</v>
       </c>
-      <c r="D122" s="7">
+      <c r="D122" s="3">
         <v>14.000000000000004</v>
       </c>
-      <c r="E122" s="7" t="s">
+      <c r="E122" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F122" s="7">
+      <c r="F122" s="3">
         <v>6679.4096000000009</v>
       </c>
-      <c r="G122" s="7">
+      <c r="G122" s="3">
         <v>1246.0000000000002</v>
       </c>
     </row>
@@ -47876,16 +47876,16 @@
       <c r="C123" s="6">
         <v>18828</v>
       </c>
-      <c r="D123" s="7">
+      <c r="D123" s="3">
         <v>14</v>
       </c>
-      <c r="E123" s="7" t="s">
+      <c r="E123" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F123" s="7">
+      <c r="F123" s="3">
         <v>10799.138400000002</v>
       </c>
-      <c r="G123" s="7">
+      <c r="G123" s="3">
         <v>1344</v>
       </c>
     </row>
@@ -47900,16 +47900,16 @@
       <c r="C124" s="6">
         <v>13450.000000000007</v>
       </c>
-      <c r="D124" s="7">
+      <c r="D124" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E124" s="7" t="s">
+      <c r="E124" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F124" s="7">
+      <c r="F124" s="3">
         <v>7715.9550000000045</v>
       </c>
-      <c r="G124" s="7">
+      <c r="G124" s="3">
         <v>960.00000000000045</v>
       </c>
     </row>
@@ -47924,16 +47924,16 @@
       <c r="C125" s="6">
         <v>21516</v>
       </c>
-      <c r="D125" s="7">
+      <c r="D125" s="3">
         <v>16</v>
       </c>
-      <c r="E125" s="7" t="s">
+      <c r="E125" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F125" s="7">
+      <c r="F125" s="3">
         <v>12342.896400000001</v>
       </c>
-      <c r="G125" s="7">
+      <c r="G125" s="3">
         <v>1536</v>
       </c>
     </row>
@@ -47948,16 +47948,16 @@
       <c r="C126" s="6">
         <v>1040.0000000000005</v>
       </c>
-      <c r="D126" s="7">
+      <c r="D126" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E126" s="7" t="s">
+      <c r="E126" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F126" s="7">
+      <c r="F126" s="3">
         <v>904.90400000000056</v>
       </c>
-      <c r="G126" s="7">
+      <c r="G126" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47972,16 +47972,16 @@
       <c r="C127" s="6">
         <v>1980.0000000000014</v>
       </c>
-      <c r="D127" s="7">
+      <c r="D127" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E127" s="7" t="s">
+      <c r="E127" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F127" s="7">
+      <c r="F127" s="3">
         <v>1727.5500000000011</v>
       </c>
-      <c r="G127" s="7">
+      <c r="G127" s="3">
         <v>0</v>
       </c>
     </row>
@@ -47996,16 +47996,16 @@
       <c r="C128" s="6">
         <v>5900.0000000000045</v>
       </c>
-      <c r="D128" s="7">
+      <c r="D128" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E128" s="7" t="s">
+      <c r="E128" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F128" s="7">
+      <c r="F128" s="3">
         <v>4392.5500000000029</v>
       </c>
-      <c r="G128" s="7">
+      <c r="G128" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48020,16 +48020,16 @@
       <c r="C129" s="6">
         <v>3780.0000000000018</v>
       </c>
-      <c r="D129" s="7">
+      <c r="D129" s="3">
         <v>12.000000000000005</v>
       </c>
-      <c r="E129" s="7" t="s">
+      <c r="E129" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F129" s="7">
+      <c r="F129" s="3">
         <v>2635.7940000000017</v>
       </c>
-      <c r="G129" s="7">
+      <c r="G129" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48044,16 +48044,16 @@
       <c r="C130" s="6">
         <v>6300.0000000000045</v>
       </c>
-      <c r="D130" s="7">
+      <c r="D130" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E130" s="7" t="s">
+      <c r="E130" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F130" s="7">
+      <c r="F130" s="3">
         <v>4392.9900000000025</v>
       </c>
-      <c r="G130" s="7">
+      <c r="G130" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48068,16 +48068,16 @@
       <c r="C131" s="6">
         <v>3200.0000000000014</v>
       </c>
-      <c r="D131" s="7">
+      <c r="D131" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E131" s="7" t="s">
+      <c r="E131" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F131" s="7">
+      <c r="F131" s="3">
         <v>2196.4800000000009</v>
       </c>
-      <c r="G131" s="7">
+      <c r="G131" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48092,16 +48092,16 @@
       <c r="C132" s="6">
         <v>2363.0000000000014</v>
       </c>
-      <c r="D132" s="7">
+      <c r="D132" s="3">
         <v>7.5000000000000053</v>
       </c>
-      <c r="E132" s="7" t="s">
+      <c r="E132" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F132" s="7">
+      <c r="F132" s="3">
         <v>1647.2473000000009</v>
       </c>
-      <c r="G132" s="7">
+      <c r="G132" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48116,16 +48116,16 @@
       <c r="C133" s="6">
         <v>4800.0000000000036</v>
       </c>
-      <c r="D133" s="7">
+      <c r="D133" s="3">
         <v>15.000000000000009</v>
       </c>
-      <c r="E133" s="7" t="s">
+      <c r="E133" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F133" s="7">
+      <c r="F133" s="3">
         <v>3294.7200000000025</v>
       </c>
-      <c r="G133" s="7">
+      <c r="G133" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48140,16 +48140,16 @@
       <c r="C134" s="6">
         <v>6400.0000000000045</v>
       </c>
-      <c r="D134" s="7">
+      <c r="D134" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E134" s="7" t="s">
+      <c r="E134" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F134" s="7">
+      <c r="F134" s="3">
         <v>4392.9600000000028</v>
       </c>
-      <c r="G134" s="7">
+      <c r="G134" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48164,16 +48164,16 @@
       <c r="C135" s="6">
         <v>6900.0000000000045</v>
       </c>
-      <c r="D135" s="7">
+      <c r="D135" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E135" s="7" t="s">
+      <c r="E135" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F135" s="7">
+      <c r="F135" s="3">
         <v>4722.3600000000033</v>
       </c>
-      <c r="G135" s="7">
+      <c r="G135" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48188,16 +48188,16 @@
       <c r="C136" s="6">
         <v>7000.0000000000045</v>
       </c>
-      <c r="D136" s="7">
+      <c r="D136" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E136" s="7" t="s">
+      <c r="E136" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F136" s="7">
+      <c r="F136" s="3">
         <v>4722.2000000000025</v>
       </c>
-      <c r="G136" s="7">
+      <c r="G136" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48212,16 +48212,16 @@
       <c r="C137" s="6">
         <v>3550.0000000000014</v>
       </c>
-      <c r="D137" s="7">
+      <c r="D137" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E137" s="7" t="s">
+      <c r="E137" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F137" s="7">
+      <c r="F137" s="3">
         <v>2361.1050000000014</v>
       </c>
-      <c r="G137" s="7">
+      <c r="G137" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48236,16 +48236,16 @@
       <c r="C138" s="6">
         <v>2663.0000000000018</v>
       </c>
-      <c r="D138" s="7">
+      <c r="D138" s="3">
         <v>7.5000000000000053</v>
       </c>
-      <c r="E138" s="7" t="s">
+      <c r="E138" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F138" s="7">
+      <c r="F138" s="3">
         <v>1770.8950000000011</v>
       </c>
-      <c r="G138" s="7">
+      <c r="G138" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48260,16 +48260,16 @@
       <c r="C139" s="6">
         <v>5325.0000000000036</v>
       </c>
-      <c r="D139" s="7">
+      <c r="D139" s="3">
         <v>15.000000000000009</v>
       </c>
-      <c r="E139" s="7" t="s">
+      <c r="E139" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F139" s="7">
+      <c r="F139" s="3">
         <v>3541.6575000000016</v>
       </c>
-      <c r="G139" s="7">
+      <c r="G139" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48284,16 +48284,16 @@
       <c r="C140" s="6">
         <v>5700.0000000000036</v>
       </c>
-      <c r="D140" s="7">
+      <c r="D140" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E140" s="7" t="s">
+      <c r="E140" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F140" s="7">
+      <c r="F140" s="3">
         <v>3926.7300000000027</v>
       </c>
-      <c r="G140" s="7">
+      <c r="G140" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48308,16 +48308,16 @@
       <c r="C141" s="6">
         <v>2213.0000000000014</v>
       </c>
-      <c r="D141" s="7">
+      <c r="D141" s="3">
         <v>7.5000000000000053</v>
       </c>
-      <c r="E141" s="7" t="s">
+      <c r="E141" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F141" s="7">
+      <c r="F141" s="3">
         <v>1477.3988000000008</v>
       </c>
-      <c r="G141" s="7">
+      <c r="G141" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48332,16 +48332,16 @@
       <c r="C142" s="6">
         <v>4929.0000000000036</v>
       </c>
-      <c r="D142" s="7">
+      <c r="D142" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E142" s="7" t="s">
+      <c r="E142" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F142" s="7">
+      <c r="F142" s="3">
         <v>4675.1565000000028</v>
       </c>
-      <c r="G142" s="7">
+      <c r="G142" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48356,16 +48356,16 @@
       <c r="C143" s="6">
         <v>6300.0000000000018</v>
       </c>
-      <c r="D143" s="7">
+      <c r="D143" s="3">
         <v>14.000000000000004</v>
       </c>
-      <c r="E143" s="7" t="s">
+      <c r="E143" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F143" s="7">
+      <c r="F143" s="3">
         <v>5137.6500000000005</v>
       </c>
-      <c r="G143" s="7">
+      <c r="G143" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48380,16 +48380,16 @@
       <c r="C144" s="6">
         <v>7200.0000000000045</v>
       </c>
-      <c r="D144" s="7">
+      <c r="D144" s="3">
         <v>16.000000000000011</v>
       </c>
-      <c r="E144" s="7" t="s">
+      <c r="E144" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F144" s="7">
+      <c r="F144" s="3">
         <v>5872.3200000000033</v>
       </c>
-      <c r="G144" s="7">
+      <c r="G144" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48404,16 +48404,16 @@
       <c r="C145" s="6">
         <v>9600.0000000000073</v>
       </c>
-      <c r="D145" s="7">
+      <c r="D145" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E145" s="7" t="s">
+      <c r="E145" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F145" s="7">
+      <c r="F145" s="3">
         <v>7899.8400000000065</v>
       </c>
-      <c r="G145" s="7">
+      <c r="G145" s="3">
         <v>0</v>
       </c>
     </row>
@@ -48428,16 +48428,16 @@
       <c r="C146" s="6">
         <v>6456.0000000000018</v>
       </c>
-      <c r="D146" s="7">
+      <c r="D146" s="3">
         <v>14.000000000000004</v>
       </c>
-      <c r="E146" s="7" t="s">
+      <c r="E146" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F146" s="7">
+      <c r="F146" s="3">
         <v>5184.1232000000009</v>
       </c>
-      <c r="G146" s="7">
+      <c r="G146" s="3">
         <v>406.00000000000011</v>
       </c>
     </row>
@@ -48452,16 +48452,16 @@
       <c r="C147" s="6">
         <v>8668.0000000000018</v>
       </c>
-      <c r="D147" s="7">
+      <c r="D147" s="3">
         <v>14.000000000000004</v>
       </c>
-      <c r="E147" s="7" t="s">
+      <c r="E147" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F147" s="7">
+      <c r="F147" s="3">
         <v>6684.6632000000009</v>
       </c>
-      <c r="G147" s="7">
+      <c r="G147" s="3">
         <v>266.00000000000006</v>
       </c>
     </row>
@@ -48476,16 +48476,16 @@
       <c r="C148" s="6">
         <v>9200.0000000000073</v>
       </c>
-      <c r="D148" s="7">
+      <c r="D148" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E148" s="7" t="s">
+      <c r="E148" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F148" s="7">
+      <c r="F148" s="3">
         <v>6238.6400000000049</v>
       </c>
-      <c r="G148" s="7">
+      <c r="G148" s="3">
         <v>180.00000000000011</v>
       </c>
     </row>
@@ -48500,16 +48500,16 @@
       <c r="C149" s="6">
         <v>9200</v>
       </c>
-      <c r="D149" s="7">
+      <c r="D149" s="3">
         <v>20</v>
       </c>
-      <c r="E149" s="7" t="s">
+      <c r="E149" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F149" s="7">
+      <c r="F149" s="3">
         <v>6230.3600000000006</v>
       </c>
-      <c r="G149" s="7">
+      <c r="G149" s="3">
         <v>180</v>
       </c>
     </row>
@@ -48524,16 +48524,16 @@
       <c r="C150" s="6">
         <v>10240</v>
       </c>
-      <c r="D150" s="7">
+      <c r="D150" s="3">
         <v>24</v>
       </c>
-      <c r="E150" s="7" t="s">
+      <c r="E150" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F150" s="7">
+      <c r="F150" s="3">
         <v>7157.8559999999998</v>
       </c>
-      <c r="G150" s="7">
+      <c r="G150" s="3">
         <v>216</v>
       </c>
     </row>
@@ -48548,16 +48548,16 @@
       <c r="C151" s="6">
         <v>3120</v>
       </c>
-      <c r="D151" s="7">
+      <c r="D151" s="3">
         <v>7</v>
       </c>
-      <c r="E151" s="7" t="s">
+      <c r="E151" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F151" s="7">
+      <c r="F151" s="3">
         <v>2139.94</v>
       </c>
-      <c r="G151" s="7">
+      <c r="G151" s="3">
         <v>77</v>
       </c>
     </row>
@@ -48572,16 +48572,16 @@
       <c r="C152" s="6">
         <v>9700.0000000000073</v>
       </c>
-      <c r="D152" s="7">
+      <c r="D152" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E152" s="7" t="s">
+      <c r="E152" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F152" s="7">
+      <c r="F152" s="3">
         <v>6506.5000000000055</v>
       </c>
-      <c r="G152" s="7">
+      <c r="G152" s="3">
         <v>380.00000000000028</v>
       </c>
     </row>
@@ -48596,16 +48596,16 @@
       <c r="C153" s="6">
         <v>9600.0000000000073</v>
       </c>
-      <c r="D153" s="7">
+      <c r="D153" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E153" s="7" t="s">
+      <c r="E153" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F153" s="7">
+      <c r="F153" s="3">
         <v>6348.480000000005</v>
       </c>
-      <c r="G153" s="7">
+      <c r="G153" s="3">
         <v>480.00000000000034</v>
       </c>
     </row>
@@ -48620,16 +48620,16 @@
       <c r="C154" s="6">
         <v>9600</v>
       </c>
-      <c r="D154" s="7">
+      <c r="D154" s="3">
         <v>20</v>
       </c>
-      <c r="E154" s="7" t="s">
+      <c r="E154" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F154" s="7">
+      <c r="F154" s="3">
         <v>6348.4800000000005</v>
       </c>
-      <c r="G154" s="7">
+      <c r="G154" s="3">
         <v>480</v>
       </c>
     </row>
@@ -48644,16 +48644,16 @@
       <c r="C155" s="6">
         <v>3320</v>
       </c>
-      <c r="D155" s="7">
+      <c r="D155" s="3">
         <v>7</v>
       </c>
-      <c r="E155" s="7" t="s">
+      <c r="E155" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F155" s="7">
+      <c r="F155" s="3">
         <v>2142.56</v>
       </c>
-      <c r="G155" s="7">
+      <c r="G155" s="3">
         <v>203</v>
       </c>
     </row>
@@ -48668,16 +48668,16 @@
       <c r="C156" s="6">
         <v>3320</v>
       </c>
-      <c r="D156" s="7">
+      <c r="D156" s="3">
         <v>7</v>
       </c>
-      <c r="E156" s="7" t="s">
+      <c r="E156" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F156" s="7">
+      <c r="F156" s="3">
         <v>2142.56</v>
       </c>
-      <c r="G156" s="7">
+      <c r="G156" s="3">
         <v>203</v>
       </c>
     </row>
@@ -48692,16 +48692,16 @@
       <c r="C157" s="6">
         <v>6850.0000000000045</v>
       </c>
-      <c r="D157" s="7">
+      <c r="D157" s="3">
         <v>15.000000000000009</v>
       </c>
-      <c r="E157" s="7" t="s">
+      <c r="E157" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F157" s="7">
+      <c r="F157" s="3">
         <v>4539.6750000000029</v>
       </c>
-      <c r="G157" s="7">
+      <c r="G157" s="3">
         <v>585.00000000000034</v>
       </c>
     </row>
@@ -48716,16 +48716,16 @@
       <c r="C158" s="6">
         <v>9400.0000000000073</v>
       </c>
-      <c r="D158" s="7">
+      <c r="D158" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E158" s="7" t="s">
+      <c r="E158" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F158" s="7">
+      <c r="F158" s="3">
         <v>6335.7600000000048</v>
       </c>
-      <c r="G158" s="7">
+      <c r="G158" s="3">
         <v>720.00000000000045</v>
       </c>
     </row>
@@ -48740,16 +48740,16 @@
       <c r="C159" s="6">
         <v>9400</v>
       </c>
-      <c r="D159" s="7">
+      <c r="D159" s="3">
         <v>20</v>
       </c>
-      <c r="E159" s="7" t="s">
+      <c r="E159" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F159" s="7">
+      <c r="F159" s="3">
         <v>6524.56</v>
       </c>
-      <c r="G159" s="7">
+      <c r="G159" s="3">
         <v>560</v>
       </c>
     </row>
@@ -48764,16 +48764,16 @@
       <c r="C160" s="6">
         <v>3451</v>
       </c>
-      <c r="D160" s="7">
+      <c r="D160" s="3">
         <v>7.5</v>
       </c>
-      <c r="E160" s="7" t="s">
+      <c r="E160" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F160" s="7">
+      <c r="F160" s="3">
         <v>2301.0768000000003</v>
       </c>
-      <c r="G160" s="7">
+      <c r="G160" s="3">
         <v>292.5</v>
       </c>
     </row>
@@ -48788,16 +48788,16 @@
       <c r="C161" s="6">
         <v>6850</v>
       </c>
-      <c r="D161" s="7">
+      <c r="D161" s="3">
         <v>15</v>
       </c>
-      <c r="E161" s="7" t="s">
+      <c r="E161" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F161" s="7">
+      <c r="F161" s="3">
         <v>4539.6750000000002</v>
       </c>
-      <c r="G161" s="7">
+      <c r="G161" s="3">
         <v>585</v>
       </c>
     </row>
@@ -48812,16 +48812,16 @@
       <c r="C162" s="6">
         <v>7600.0000000000055</v>
       </c>
-      <c r="D162" s="7">
+      <c r="D162" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E162" s="7" t="s">
+      <c r="E162" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F162" s="7">
+      <c r="F162" s="3">
         <v>5753.8000000000038</v>
       </c>
-      <c r="G162" s="7">
+      <c r="G162" s="3">
         <v>80.000000000000057</v>
       </c>
     </row>
@@ -48836,16 +48836,16 @@
       <c r="C163" s="6">
         <v>2476.0000000000018</v>
       </c>
-      <c r="D163" s="7">
+      <c r="D163" s="3">
         <v>7.5000000000000053</v>
       </c>
-      <c r="E163" s="7" t="s">
+      <c r="E163" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F163" s="7">
+      <c r="F163" s="3">
         <v>1889.2652000000012</v>
       </c>
-      <c r="G163" s="7">
+      <c r="G163" s="3">
         <v>67.500000000000043</v>
       </c>
     </row>
@@ -48860,16 +48860,16 @@
       <c r="C164" s="6">
         <v>4950.0000000000036</v>
       </c>
-      <c r="D164" s="7">
+      <c r="D164" s="3">
         <v>15.000000000000009</v>
       </c>
-      <c r="E164" s="7" t="s">
+      <c r="E164" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F164" s="7">
+      <c r="F164" s="3">
         <v>3767.5350000000026</v>
       </c>
-      <c r="G164" s="7">
+      <c r="G164" s="3">
         <v>135.00000000000009</v>
       </c>
     </row>
@@ -48884,16 +48884,16 @@
       <c r="C165" s="6">
         <v>7280.0000000000055</v>
       </c>
-      <c r="D165" s="7">
+      <c r="D165" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E165" s="7" t="s">
+      <c r="E165" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F165" s="7">
+      <c r="F165" s="3">
         <v>5484.2640000000038</v>
       </c>
-      <c r="G165" s="7">
+      <c r="G165" s="3">
         <v>80.000000000000057</v>
       </c>
     </row>
@@ -48908,16 +48908,16 @@
       <c r="C166" s="6">
         <v>4260.0000000000018</v>
       </c>
-      <c r="D166" s="7">
+      <c r="D166" s="3">
         <v>12.000000000000005</v>
       </c>
-      <c r="E166" s="7" t="s">
+      <c r="E166" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F166" s="7">
+      <c r="F166" s="3">
         <v>3243.5820000000017</v>
       </c>
-      <c r="G166" s="7">
+      <c r="G166" s="3">
         <v>48.000000000000021</v>
       </c>
     </row>
@@ -48932,16 +48932,16 @@
       <c r="C167" s="6">
         <v>7080.0000000000045</v>
       </c>
-      <c r="D167" s="7">
+      <c r="D167" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E167" s="7" t="s">
+      <c r="E167" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F167" s="7">
+      <c r="F167" s="3">
         <v>5375.6080000000047</v>
       </c>
-      <c r="G167" s="7">
+      <c r="G167" s="3">
         <v>80.000000000000057</v>
       </c>
     </row>
@@ -48956,16 +48956,16 @@
       <c r="C168" s="6">
         <v>2591.0000000000018</v>
       </c>
-      <c r="D168" s="7">
+      <c r="D168" s="3">
         <v>7.5000000000000053</v>
       </c>
-      <c r="E168" s="7" t="s">
+      <c r="E168" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F168" s="7">
+      <c r="F168" s="3">
         <v>1942.1073000000017</v>
       </c>
-      <c r="G168" s="7">
+      <c r="G168" s="3">
         <v>67.500000000000043</v>
       </c>
     </row>
@@ -48980,16 +48980,16 @@
       <c r="C169" s="6">
         <v>5150.0000000000036</v>
       </c>
-      <c r="D169" s="7">
+      <c r="D169" s="3">
         <v>15.000000000000009</v>
       </c>
-      <c r="E169" s="7" t="s">
+      <c r="E169" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F169" s="7">
+      <c r="F169" s="3">
         <v>3840.7050000000027</v>
       </c>
-      <c r="G169" s="7">
+      <c r="G169" s="3">
         <v>135.00000000000009</v>
       </c>
     </row>
@@ -49004,16 +49004,16 @@
       <c r="C170" s="6">
         <v>5040.0000000000018</v>
       </c>
-      <c r="D170" s="7">
+      <c r="D170" s="3">
         <v>12.000000000000005</v>
       </c>
-      <c r="E170" s="7" t="s">
+      <c r="E170" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F170" s="7">
+      <c r="F170" s="3">
         <v>4148.4240000000018</v>
       </c>
-      <c r="G170" s="7">
+      <c r="G170" s="3">
         <v>0</v>
       </c>
     </row>
@@ -49028,16 +49028,16 @@
       <c r="C171" s="6">
         <v>7300.0000000000055</v>
       </c>
-      <c r="D171" s="7">
+      <c r="D171" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E171" s="7" t="s">
+      <c r="E171" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F171" s="7">
+      <c r="F171" s="3">
         <v>6052.4300000000039</v>
       </c>
-      <c r="G171" s="7">
+      <c r="G171" s="3">
         <v>0</v>
       </c>
     </row>
@@ -49052,16 +49052,16 @@
       <c r="C172" s="6">
         <v>7160.0000000000036</v>
       </c>
-      <c r="D172" s="7">
+      <c r="D172" s="3">
         <v>20.000000000000011</v>
       </c>
-      <c r="E172" s="7" t="s">
+      <c r="E172" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F172" s="7">
+      <c r="F172" s="3">
         <v>5695.0640000000039</v>
       </c>
-      <c r="G172" s="7">
+      <c r="G172" s="3">
         <v>0</v>
       </c>
     </row>
@@ -49076,16 +49076,16 @@
       <c r="C173" s="6">
         <v>6940.0000000000045</v>
       </c>
-      <c r="D173" s="7">
+      <c r="D173" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E173" s="7" t="s">
+      <c r="E173" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F173" s="7">
+      <c r="F173" s="3">
         <v>5481.1960000000036</v>
       </c>
-      <c r="G173" s="7">
+      <c r="G173" s="3">
         <v>80.000000000000057</v>
       </c>
     </row>
@@ -49100,16 +49100,16 @@
       <c r="C174" s="6">
         <v>6920.0000000000045</v>
       </c>
-      <c r="D174" s="7">
+      <c r="D174" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E174" s="7" t="s">
+      <c r="E174" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F174" s="7">
+      <c r="F174" s="3">
         <v>5077.2200000000039</v>
       </c>
-      <c r="G174" s="7">
+      <c r="G174" s="3">
         <v>380.00000000000028</v>
       </c>
     </row>
@@ -49124,16 +49124,16 @@
       <c r="C175" s="6">
         <v>3340.0000000000014</v>
       </c>
-      <c r="D175" s="7">
+      <c r="D175" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E175" s="7" t="s">
+      <c r="E175" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F175" s="7">
+      <c r="F175" s="3">
         <v>2493.2240000000011</v>
       </c>
-      <c r="G175" s="7">
+      <c r="G175" s="3">
         <v>190.00000000000011</v>
       </c>
     </row>
@@ -49148,16 +49148,16 @@
       <c r="C176" s="6">
         <v>2514.0000000000018</v>
       </c>
-      <c r="D176" s="7">
+      <c r="D176" s="3">
         <v>7.5000000000000053</v>
       </c>
-      <c r="E176" s="7" t="s">
+      <c r="E176" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F176" s="7">
+      <c r="F176" s="3">
         <v>1881.7656000000015</v>
       </c>
-      <c r="G176" s="7">
+      <c r="G176" s="3">
         <v>142.50000000000011</v>
       </c>
     </row>
@@ -49172,16 +49172,16 @@
       <c r="C177" s="6">
         <v>6640.0000000000045</v>
       </c>
-      <c r="D177" s="7">
+      <c r="D177" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E177" s="7" t="s">
+      <c r="E177" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F177" s="7">
+      <c r="F177" s="3">
         <v>4889.4960000000037</v>
       </c>
-      <c r="G177" s="7">
+      <c r="G177" s="3">
         <v>380.00000000000028</v>
       </c>
     </row>
@@ -49196,16 +49196,16 @@
       <c r="C178" s="6">
         <v>8800.0000000000055</v>
       </c>
-      <c r="D178" s="7">
+      <c r="D178" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E178" s="7" t="s">
+      <c r="E178" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F178" s="7">
+      <c r="F178" s="3">
         <v>6310.640000000004</v>
       </c>
-      <c r="G178" s="7">
+      <c r="G178" s="3">
         <v>680.00000000000045</v>
       </c>
     </row>
@@ -49220,16 +49220,16 @@
       <c r="C179" s="6">
         <v>5240.0000000000027</v>
       </c>
-      <c r="D179" s="7">
+      <c r="D179" s="3">
         <v>12.000000000000005</v>
       </c>
-      <c r="E179" s="7" t="s">
+      <c r="E179" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F179" s="7">
+      <c r="F179" s="3">
         <v>3759.8160000000016</v>
       </c>
-      <c r="G179" s="7">
+      <c r="G179" s="3">
         <v>408.00000000000017</v>
       </c>
     </row>
@@ -49244,16 +49244,16 @@
       <c r="C180" s="6">
         <v>8600.0000000000055</v>
       </c>
-      <c r="D180" s="7">
+      <c r="D180" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E180" s="7" t="s">
+      <c r="E180" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F180" s="7">
+      <c r="F180" s="3">
         <v>6005.0000000000036</v>
       </c>
-      <c r="G180" s="7">
+      <c r="G180" s="3">
         <v>880.00000000000068</v>
       </c>
     </row>
@@ -49268,16 +49268,16 @@
       <c r="C181" s="6">
         <v>4250</v>
       </c>
-      <c r="D181" s="7">
+      <c r="D181" s="3">
         <v>10</v>
       </c>
-      <c r="E181" s="7" t="s">
+      <c r="E181" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F181" s="7">
+      <c r="F181" s="3">
         <v>2978.9750000000004</v>
       </c>
-      <c r="G181" s="7">
+      <c r="G181" s="3">
         <v>440</v>
       </c>
     </row>
@@ -49292,16 +49292,16 @@
       <c r="C182" s="6">
         <v>3201</v>
       </c>
-      <c r="D182" s="7">
+      <c r="D182" s="3">
         <v>7.5</v>
       </c>
-      <c r="E182" s="7" t="s">
+      <c r="E182" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F182" s="7">
+      <c r="F182" s="3">
         <v>2242.1420999999996</v>
       </c>
-      <c r="G182" s="7">
+      <c r="G182" s="3">
         <v>330</v>
       </c>
     </row>
@@ -49316,16 +49316,16 @@
       <c r="C183" s="6">
         <v>6350</v>
       </c>
-      <c r="D183" s="7">
+      <c r="D183" s="3">
         <v>15</v>
       </c>
-      <c r="E183" s="7" t="s">
+      <c r="E183" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F183" s="7">
+      <c r="F183" s="3">
         <v>4432.6449999999995</v>
       </c>
-      <c r="G183" s="7">
+      <c r="G183" s="3">
         <v>660</v>
       </c>
     </row>
@@ -49340,16 +49340,16 @@
       <c r="C184" s="6">
         <v>8400.0000000000055</v>
       </c>
-      <c r="D184" s="7">
+      <c r="D184" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E184" s="7" t="s">
+      <c r="E184" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F184" s="7">
+      <c r="F184" s="3">
         <v>5894.1200000000044</v>
       </c>
-      <c r="G184" s="7">
+      <c r="G184" s="3">
         <v>880.00000000000068</v>
       </c>
     </row>
@@ -49364,16 +49364,16 @@
       <c r="C185" s="6">
         <v>7960.0000000000045</v>
       </c>
-      <c r="D185" s="7">
+      <c r="D185" s="3">
         <v>20.000000000000011</v>
       </c>
-      <c r="E185" s="7" t="s">
+      <c r="E185" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F185" s="7">
+      <c r="F185" s="3">
         <v>6646.6000000000031</v>
       </c>
-      <c r="G185" s="7">
+      <c r="G185" s="3">
         <v>0</v>
       </c>
     </row>
@@ -49388,16 +49388,16 @@
       <c r="C186" s="6">
         <v>7500.0000000000055</v>
       </c>
-      <c r="D186" s="7">
+      <c r="D186" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E186" s="7" t="s">
+      <c r="E186" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F186" s="7">
+      <c r="F186" s="3">
         <v>6230.2500000000045</v>
       </c>
-      <c r="G186" s="7">
+      <c r="G186" s="3">
         <v>0</v>
       </c>
     </row>
@@ -49412,16 +49412,16 @@
       <c r="C187" s="6">
         <v>7300.0000000000045</v>
       </c>
-      <c r="D187" s="7">
+      <c r="D187" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E187" s="7" t="s">
+      <c r="E187" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F187" s="7">
+      <c r="F187" s="3">
         <v>6220.3300000000045</v>
       </c>
-      <c r="G187" s="7">
+      <c r="G187" s="3">
         <v>0</v>
       </c>
     </row>
@@ -49436,16 +49436,16 @@
       <c r="C188" s="6">
         <v>3320.0000000000014</v>
       </c>
-      <c r="D188" s="7">
+      <c r="D188" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E188" s="7" t="s">
+      <c r="E188" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F188" s="7">
+      <c r="F188" s="3">
         <v>2832.2920000000013</v>
       </c>
-      <c r="G188" s="7">
+      <c r="G188" s="3">
         <v>0</v>
       </c>
     </row>
@@ -49460,16 +49460,16 @@
       <c r="C189" s="6">
         <v>2738.0000000000018</v>
       </c>
-      <c r="D189" s="7">
+      <c r="D189" s="3">
         <v>7.5000000000000053</v>
       </c>
-      <c r="E189" s="7" t="s">
+      <c r="E189" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F189" s="7">
+      <c r="F189" s="3">
         <v>2327.5738000000015</v>
       </c>
-      <c r="G189" s="7">
+      <c r="G189" s="3">
         <v>0</v>
       </c>
     </row>
@@ -49484,16 +49484,16 @@
       <c r="C190" s="6">
         <v>7200.0000000000045</v>
       </c>
-      <c r="D190" s="7">
+      <c r="D190" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E190" s="7" t="s">
+      <c r="E190" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F190" s="7">
+      <c r="F190" s="3">
         <v>6163.9200000000046</v>
       </c>
-      <c r="G190" s="7">
+      <c r="G190" s="3">
         <v>0</v>
       </c>
     </row>
@@ -49508,16 +49508,16 @@
       <c r="C191" s="6">
         <v>3804</v>
       </c>
-      <c r="D191" s="7">
+      <c r="D191" s="3">
         <v>10</v>
       </c>
-      <c r="E191" s="7" t="s">
+      <c r="E191" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F191" s="7">
+      <c r="F191" s="3">
         <v>2967.0516000000007</v>
       </c>
-      <c r="G191" s="7">
+      <c r="G191" s="3">
         <v>90</v>
       </c>
     </row>
@@ -49532,16 +49532,16 @@
       <c r="C192" s="6">
         <v>8700.0000000000055</v>
       </c>
-      <c r="D192" s="7">
+      <c r="D192" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E192" s="7" t="s">
+      <c r="E192" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F192" s="7">
+      <c r="F192" s="3">
         <v>6383.1600000000035</v>
       </c>
-      <c r="G192" s="7">
+      <c r="G192" s="3">
         <v>480.00000000000034</v>
       </c>
     </row>
@@ -49556,16 +49556,16 @@
       <c r="C193" s="6">
         <v>8400.0000000000055</v>
       </c>
-      <c r="D193" s="7">
+      <c r="D193" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E193" s="7" t="s">
+      <c r="E193" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F193" s="7">
+      <c r="F193" s="3">
         <v>6088.5200000000032</v>
       </c>
-      <c r="G193" s="7">
+      <c r="G193" s="3">
         <v>580.00000000000045</v>
       </c>
     </row>
@@ -49580,16 +49580,16 @@
       <c r="C194" s="6">
         <v>8400</v>
       </c>
-      <c r="D194" s="7">
+      <c r="D194" s="3">
         <v>20</v>
       </c>
-      <c r="E194" s="7" t="s">
+      <c r="E194" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F194" s="7">
+      <c r="F194" s="3">
         <v>6088.5199999999995</v>
       </c>
-      <c r="G194" s="7">
+      <c r="G194" s="3">
         <v>580</v>
       </c>
     </row>
@@ -49604,16 +49604,16 @@
       <c r="C195" s="6">
         <v>3101.0000000000023</v>
       </c>
-      <c r="D195" s="7">
+      <c r="D195" s="3">
         <v>7.5000000000000053</v>
       </c>
-      <c r="E195" s="7" t="s">
+      <c r="E195" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F195" s="7">
+      <c r="F195" s="3">
         <v>2257.0206000000012</v>
       </c>
-      <c r="G195" s="7">
+      <c r="G195" s="3">
         <v>217.50000000000014</v>
       </c>
     </row>
@@ -49628,16 +49628,16 @@
       <c r="C196" s="6">
         <v>8100</v>
       </c>
-      <c r="D196" s="7">
+      <c r="D196" s="3">
         <v>20</v>
       </c>
-      <c r="E196" s="7" t="s">
+      <c r="E196" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F196" s="7">
+      <c r="F196" s="3">
         <v>5636</v>
       </c>
-      <c r="G196" s="7">
+      <c r="G196" s="3">
         <v>880</v>
       </c>
     </row>
@@ -49652,16 +49652,16 @@
       <c r="C197" s="6">
         <v>9800.0000000000073</v>
       </c>
-      <c r="D197" s="7">
+      <c r="D197" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E197" s="7" t="s">
+      <c r="E197" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F197" s="7">
+      <c r="F197" s="3">
         <v>7015.860000000006</v>
       </c>
-      <c r="G197" s="7">
+      <c r="G197" s="3">
         <v>480.00000000000034</v>
       </c>
     </row>
@@ -49676,16 +49676,16 @@
       <c r="C198" s="6">
         <v>8400</v>
       </c>
-      <c r="D198" s="7">
+      <c r="D198" s="3">
         <v>20</v>
       </c>
-      <c r="E198" s="7" t="s">
+      <c r="E198" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F198" s="7">
+      <c r="F198" s="3">
         <v>6184.28</v>
       </c>
-      <c r="G198" s="7">
+      <c r="G198" s="3">
         <v>580</v>
       </c>
     </row>
@@ -49700,16 +49700,16 @@
       <c r="C199" s="6">
         <v>8850.0000000000055</v>
       </c>
-      <c r="D199" s="7">
+      <c r="D199" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E199" s="7" t="s">
+      <c r="E199" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F199" s="7">
+      <c r="F199" s="3">
         <v>6232.7600000000039</v>
       </c>
-      <c r="G199" s="7">
+      <c r="G199" s="3">
         <v>880.00000000000068</v>
       </c>
     </row>
@@ -49724,16 +49724,16 @@
       <c r="C200" s="6">
         <v>8850</v>
       </c>
-      <c r="D200" s="7">
+      <c r="D200" s="3">
         <v>20</v>
       </c>
-      <c r="E200" s="7" t="s">
+      <c r="E200" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F200" s="7">
+      <c r="F200" s="3">
         <v>6232.7599999999993</v>
       </c>
-      <c r="G200" s="7">
+      <c r="G200" s="3">
         <v>880</v>
       </c>
     </row>
@@ -49748,16 +49748,16 @@
       <c r="C201" s="6">
         <v>7560</v>
       </c>
-      <c r="D201" s="7">
+      <c r="D201" s="3">
         <v>24</v>
       </c>
-      <c r="E201" s="7" t="s">
+      <c r="E201" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F201" s="7">
+      <c r="F201" s="3">
         <v>6150.0599999999986</v>
       </c>
-      <c r="G201" s="7">
+      <c r="G201" s="3">
         <v>0</v>
       </c>
     </row>
@@ -49772,16 +49772,16 @@
       <c r="C202" s="6">
         <v>5364.0000000000009</v>
       </c>
-      <c r="D202" s="7">
+      <c r="D202" s="3">
         <v>14.000000000000004</v>
       </c>
-      <c r="E202" s="7" t="s">
+      <c r="E202" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F202" s="7">
+      <c r="F202" s="3">
         <v>3712.8804000000005</v>
       </c>
-      <c r="G202" s="7">
+      <c r="G202" s="3">
         <v>336.00000000000011</v>
       </c>
     </row>
@@ -49796,16 +49796,16 @@
       <c r="C203" s="6">
         <v>2788.0000000000018</v>
       </c>
-      <c r="D203" s="7">
+      <c r="D203" s="3">
         <v>7.5000000000000053</v>
       </c>
-      <c r="E203" s="7" t="s">
+      <c r="E203" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F203" s="7">
+      <c r="F203" s="3">
         <v>2384.2976000000012</v>
       </c>
-      <c r="G203" s="7">
+      <c r="G203" s="3">
         <v>0</v>
       </c>
     </row>
@@ -49820,16 +49820,16 @@
       <c r="C204" s="6">
         <v>3183</v>
       </c>
-      <c r="D204" s="7">
+      <c r="D204" s="3">
         <v>8.5</v>
       </c>
-      <c r="E204" s="7" t="s">
+      <c r="E204" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F204" s="7">
+      <c r="F204" s="3">
         <v>2704.9133999999999</v>
       </c>
-      <c r="G204" s="7">
+      <c r="G204" s="3">
         <v>0</v>
       </c>
     </row>
@@ -49844,16 +49844,16 @@
       <c r="C205" s="6">
         <v>8000.0000000000055</v>
       </c>
-      <c r="D205" s="7">
+      <c r="D205" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E205" s="7" t="s">
+      <c r="E205" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F205" s="7">
+      <c r="F205" s="3">
         <v>6250.8000000000047</v>
       </c>
-      <c r="G205" s="7">
+      <c r="G205" s="3">
         <v>180.00000000000011</v>
       </c>
     </row>
@@ -49868,16 +49868,16 @@
       <c r="C206" s="6">
         <v>4720.0000000000018</v>
       </c>
-      <c r="D206" s="7">
+      <c r="D206" s="3">
         <v>12.000000000000005</v>
       </c>
-      <c r="E206" s="7" t="s">
+      <c r="E206" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F206" s="7">
+      <c r="F206" s="3">
         <v>3342.2320000000018</v>
       </c>
-      <c r="G206" s="7">
+      <c r="G206" s="3">
         <v>420.00000000000017</v>
       </c>
     </row>
@@ -49892,16 +49892,16 @@
       <c r="C207" s="6">
         <v>4720</v>
       </c>
-      <c r="D207" s="7">
+      <c r="D207" s="3">
         <v>12</v>
       </c>
-      <c r="E207" s="7" t="s">
+      <c r="E207" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F207" s="7">
+      <c r="F207" s="3">
         <v>3342.2320000000004</v>
       </c>
-      <c r="G207" s="7">
+      <c r="G207" s="3">
         <v>420</v>
       </c>
     </row>
@@ -49916,16 +49916,16 @@
       <c r="C208" s="6">
         <v>7800.0000000000055</v>
       </c>
-      <c r="D208" s="7">
+      <c r="D208" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E208" s="7" t="s">
+      <c r="E208" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F208" s="7">
+      <c r="F208" s="3">
         <v>5881.100000000004</v>
       </c>
-      <c r="G208" s="7">
+      <c r="G208" s="3">
         <v>400.00000000000028</v>
       </c>
     </row>
@@ -49940,16 +49940,16 @@
       <c r="C209" s="6">
         <v>3850</v>
       </c>
-      <c r="D209" s="7">
+      <c r="D209" s="3">
         <v>10</v>
       </c>
-      <c r="E209" s="7" t="s">
+      <c r="E209" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F209" s="7">
+      <c r="F209" s="3">
         <v>2791.0650000000001</v>
       </c>
-      <c r="G209" s="7">
+      <c r="G209" s="3">
         <v>300</v>
       </c>
     </row>
@@ -49964,16 +49964,16 @@
       <c r="C210" s="6">
         <v>3850.0000000000018</v>
       </c>
-      <c r="D210" s="7">
+      <c r="D210" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E210" s="7" t="s">
+      <c r="E210" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F210" s="7">
+      <c r="F210" s="3">
         <v>2673.0650000000014</v>
       </c>
-      <c r="G210" s="7">
+      <c r="G210" s="3">
         <v>400.00000000000023</v>
       </c>
     </row>
@@ -49988,16 +49988,16 @@
       <c r="C211" s="6">
         <v>2901</v>
       </c>
-      <c r="D211" s="7">
+      <c r="D211" s="3">
         <v>7.5</v>
       </c>
-      <c r="E211" s="7" t="s">
+      <c r="E211" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F211" s="7">
+      <c r="F211" s="3">
         <v>2061.8175000000001</v>
       </c>
-      <c r="G211" s="7">
+      <c r="G211" s="3">
         <v>262.5</v>
       </c>
     </row>
@@ -50012,16 +50012,16 @@
       <c r="C212" s="6">
         <v>2901.0000000000018</v>
       </c>
-      <c r="D212" s="7">
+      <c r="D212" s="3">
         <v>7.5000000000000053</v>
       </c>
-      <c r="E212" s="7" t="s">
+      <c r="E212" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F212" s="7">
+      <c r="F212" s="3">
         <v>1973.3175000000015</v>
       </c>
-      <c r="G212" s="7">
+      <c r="G212" s="3">
         <v>337.50000000000023</v>
       </c>
     </row>
@@ -50036,16 +50036,16 @@
       <c r="C213" s="6">
         <v>5700</v>
       </c>
-      <c r="D213" s="7">
+      <c r="D213" s="3">
         <v>15</v>
       </c>
-      <c r="E213" s="7" t="s">
+      <c r="E213" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F213" s="7">
+      <c r="F213" s="3">
         <v>4084.1400000000003</v>
       </c>
-      <c r="G213" s="7">
+      <c r="G213" s="3">
         <v>525</v>
       </c>
     </row>
@@ -50060,16 +50060,16 @@
       <c r="C214" s="6">
         <v>7600.0000000000055</v>
       </c>
-      <c r="D214" s="7">
+      <c r="D214" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E214" s="7" t="s">
+      <c r="E214" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F214" s="7">
+      <c r="F214" s="3">
         <v>5316.1200000000035</v>
       </c>
-      <c r="G214" s="7">
+      <c r="G214" s="3">
         <v>800.00000000000057</v>
       </c>
     </row>
@@ -50084,16 +50084,16 @@
       <c r="C215" s="6">
         <v>2751</v>
       </c>
-      <c r="D215" s="7">
+      <c r="D215" s="3">
         <v>7.5</v>
       </c>
-      <c r="E215" s="7" t="s">
+      <c r="E215" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F215" s="7">
+      <c r="F215" s="3">
         <v>1975.7865000000004</v>
       </c>
-      <c r="G215" s="7">
+      <c r="G215" s="3">
         <v>217.5</v>
       </c>
     </row>
@@ -50108,16 +50108,16 @@
       <c r="C216" s="6">
         <v>8240.0000000000036</v>
       </c>
-      <c r="D216" s="7">
+      <c r="D216" s="3">
         <v>20.000000000000011</v>
       </c>
-      <c r="E216" s="7" t="s">
+      <c r="E216" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F216" s="7">
+      <c r="F216" s="3">
         <v>6394.8960000000034</v>
       </c>
-      <c r="G216" s="7">
+      <c r="G216" s="3">
         <v>100.00000000000006</v>
       </c>
     </row>
@@ -50132,16 +50132,16 @@
       <c r="C217" s="6">
         <v>7800.0000000000055</v>
       </c>
-      <c r="D217" s="7">
+      <c r="D217" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E217" s="7" t="s">
+      <c r="E217" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F217" s="7">
+      <c r="F217" s="3">
         <v>6228.8600000000042</v>
       </c>
-      <c r="G217" s="7">
+      <c r="G217" s="3">
         <v>100.00000000000007</v>
       </c>
     </row>
@@ -50156,16 +50156,16 @@
       <c r="C218" s="6">
         <v>4640.0000000000018</v>
       </c>
-      <c r="D218" s="7">
+      <c r="D218" s="3">
         <v>12.000000000000005</v>
       </c>
-      <c r="E218" s="7" t="s">
+      <c r="E218" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F218" s="7">
+      <c r="F218" s="3">
         <v>3552.4960000000015</v>
       </c>
-      <c r="G218" s="7">
+      <c r="G218" s="3">
         <v>180.00000000000009</v>
       </c>
     </row>
@@ -50180,16 +50180,16 @@
       <c r="C219" s="6">
         <v>7680.0000000000055</v>
       </c>
-      <c r="D219" s="7">
+      <c r="D219" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E219" s="7" t="s">
+      <c r="E219" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F219" s="7">
+      <c r="F219" s="3">
         <v>5683.024000000004</v>
       </c>
-      <c r="G219" s="7">
+      <c r="G219" s="3">
         <v>500.00000000000034</v>
       </c>
     </row>
@@ -50204,16 +50204,16 @@
       <c r="C220" s="6">
         <v>3800.0000000000018</v>
       </c>
-      <c r="D220" s="7">
+      <c r="D220" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E220" s="7" t="s">
+      <c r="E220" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F220" s="7">
+      <c r="F220" s="3">
         <v>2827.4600000000019</v>
       </c>
-      <c r="G220" s="7">
+      <c r="G220" s="3">
         <v>250.00000000000014</v>
       </c>
     </row>
@@ -50228,16 +50228,16 @@
       <c r="C221" s="6">
         <v>2851.0000000000018</v>
       </c>
-      <c r="D221" s="7">
+      <c r="D221" s="3">
         <v>7.5000000000000053</v>
       </c>
-      <c r="E221" s="7" t="s">
+      <c r="E221" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F221" s="7">
+      <c r="F221" s="3">
         <v>2120.5614000000014</v>
       </c>
-      <c r="G221" s="7">
+      <c r="G221" s="3">
         <v>187.50000000000014</v>
       </c>
     </row>
@@ -50252,16 +50252,16 @@
       <c r="C222" s="6">
         <v>5700.0000000000036</v>
       </c>
-      <c r="D222" s="7">
+      <c r="D222" s="3">
         <v>15.000000000000009</v>
       </c>
-      <c r="E222" s="7" t="s">
+      <c r="E222" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F222" s="7">
+      <c r="F222" s="3">
         <v>4321.1400000000031</v>
       </c>
-      <c r="G222" s="7">
+      <c r="G222" s="3">
         <v>300.00000000000017</v>
       </c>
     </row>
@@ -50276,16 +50276,16 @@
       <c r="C223" s="6">
         <v>7500.0000000000045</v>
       </c>
-      <c r="D223" s="7">
+      <c r="D223" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E223" s="7" t="s">
+      <c r="E223" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F223" s="7">
+      <c r="F223" s="3">
         <v>5529.2500000000027</v>
       </c>
-      <c r="G223" s="7">
+      <c r="G223" s="3">
         <v>500.00000000000034</v>
       </c>
     </row>
@@ -50300,16 +50300,16 @@
       <c r="C224" s="6">
         <v>2310</v>
       </c>
-      <c r="D224" s="7">
+      <c r="D224" s="3">
         <v>5</v>
       </c>
-      <c r="E224" s="7" t="s">
+      <c r="E224" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F224" s="7">
+      <c r="F224" s="3">
         <v>1811.5020000000002</v>
       </c>
-      <c r="G224" s="7">
+      <c r="G224" s="3">
         <v>0</v>
       </c>
     </row>
@@ -50324,16 +50324,16 @@
       <c r="C225" s="6">
         <v>4520.0000000000027</v>
       </c>
-      <c r="D225" s="7">
+      <c r="D225" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E225" s="7" t="s">
+      <c r="E225" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F225" s="7">
+      <c r="F225" s="3">
         <v>3623.2320000000018</v>
       </c>
-      <c r="G225" s="7">
+      <c r="G225" s="3">
         <v>0</v>
       </c>
     </row>
@@ -50348,16 +50348,16 @@
       <c r="C226" s="6">
         <v>8300.0000000000055</v>
       </c>
-      <c r="D226" s="7">
+      <c r="D226" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E226" s="7" t="s">
+      <c r="E226" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F226" s="7">
+      <c r="F226" s="3">
         <v>6696.440000000006</v>
       </c>
-      <c r="G226" s="7">
+      <c r="G226" s="3">
         <v>0</v>
       </c>
     </row>
@@ -50372,16 +50372,16 @@
       <c r="C227" s="6">
         <v>4150.0000000000018</v>
       </c>
-      <c r="D227" s="7">
+      <c r="D227" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E227" s="7" t="s">
+      <c r="E227" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F227" s="7">
+      <c r="F227" s="3">
         <v>3348.2200000000025</v>
       </c>
-      <c r="G227" s="7">
+      <c r="G227" s="3">
         <v>0</v>
       </c>
     </row>
@@ -50396,16 +50396,16 @@
       <c r="C228" s="6">
         <v>6468.0000000000045</v>
       </c>
-      <c r="D228" s="7">
+      <c r="D228" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E228" s="7" t="s">
+      <c r="E228" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F228" s="7">
+      <c r="F228" s="3">
         <v>5363.9124000000038</v>
       </c>
-      <c r="G228" s="7">
+      <c r="G228" s="3">
         <v>0</v>
       </c>
     </row>
@@ -50420,16 +50420,16 @@
       <c r="C229" s="6">
         <v>3193.0000000000014</v>
       </c>
-      <c r="D229" s="7">
+      <c r="D229" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E229" s="7" t="s">
+      <c r="E229" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F229" s="7">
+      <c r="F229" s="3">
         <v>2649.2321000000015</v>
       </c>
-      <c r="G229" s="7">
+      <c r="G229" s="3">
         <v>0</v>
       </c>
     </row>
@@ -50444,16 +50444,16 @@
       <c r="C230" s="6">
         <v>6277.0000000000045</v>
       </c>
-      <c r="D230" s="7">
+      <c r="D230" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E230" s="7" t="s">
+      <c r="E230" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F230" s="7">
+      <c r="F230" s="3">
         <v>5211.1654000000044</v>
       </c>
-      <c r="G230" s="7">
+      <c r="G230" s="3">
         <v>0</v>
       </c>
     </row>
@@ -50468,16 +50468,16 @@
       <c r="C231" s="6">
         <v>6780.0000000000045</v>
       </c>
-      <c r="D231" s="7">
+      <c r="D231" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E231" s="7" t="s">
+      <c r="E231" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F231" s="7">
+      <c r="F231" s="3">
         <v>5105.9900000000034</v>
       </c>
-      <c r="G231" s="7">
+      <c r="G231" s="3">
         <v>100.00000000000007</v>
       </c>
     </row>
@@ -50492,16 +50492,16 @@
       <c r="C232" s="6">
         <v>4068.0000000000018</v>
       </c>
-      <c r="D232" s="7">
+      <c r="D232" s="3">
         <v>12.000000000000005</v>
       </c>
-      <c r="E232" s="7" t="s">
+      <c r="E232" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F232" s="7">
+      <c r="F232" s="3">
         <v>2867.6556000000014</v>
       </c>
-      <c r="G232" s="7">
+      <c r="G232" s="3">
         <v>144.00000000000006</v>
       </c>
     </row>
@@ -50516,16 +50516,16 @@
       <c r="C233" s="6">
         <v>6300.0000000000045</v>
       </c>
-      <c r="D233" s="7">
+      <c r="D233" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E233" s="7" t="s">
+      <c r="E233" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F233" s="7">
+      <c r="F233" s="3">
         <v>5096.7000000000035</v>
       </c>
-      <c r="G233" s="7">
+      <c r="G233" s="3">
         <v>0</v>
       </c>
     </row>
@@ -50540,16 +50540,16 @@
       <c r="C234" s="6">
         <v>3150.0000000000018</v>
       </c>
-      <c r="D234" s="7">
+      <c r="D234" s="3">
         <v>10.000000000000005</v>
       </c>
-      <c r="E234" s="7" t="s">
+      <c r="E234" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F234" s="7">
+      <c r="F234" s="3">
         <v>2548.3500000000013</v>
       </c>
-      <c r="G234" s="7">
+      <c r="G234" s="3">
         <v>0</v>
       </c>
     </row>
@@ -50564,16 +50564,16 @@
       <c r="C235" s="6">
         <v>8400.0000000000055</v>
       </c>
-      <c r="D235" s="7">
+      <c r="D235" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E235" s="7" t="s">
+      <c r="E235" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F235" s="7">
+      <c r="F235" s="3">
         <v>6916.5600000000049</v>
       </c>
-      <c r="G235" s="7">
+      <c r="G235" s="3">
         <v>0</v>
       </c>
     </row>
@@ -50588,16 +50588,16 @@
       <c r="C236" s="6">
         <v>6048.0000000000036</v>
       </c>
-      <c r="D236" s="7">
+      <c r="D236" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E236" s="7" t="s">
+      <c r="E236" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F236" s="7">
+      <c r="F236" s="3">
         <v>4881.3408000000036</v>
       </c>
-      <c r="G236" s="7">
+      <c r="G236" s="3">
         <v>0</v>
       </c>
     </row>
@@ -50612,16 +50612,16 @@
       <c r="C237" s="6">
         <v>4860.0000000000009</v>
       </c>
-      <c r="D237" s="7">
+      <c r="D237" s="3">
         <v>14.000000000000004</v>
       </c>
-      <c r="E237" s="7" t="s">
+      <c r="E237" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F237" s="7">
+      <c r="F237" s="3">
         <v>3687.3380000000006</v>
       </c>
-      <c r="G237" s="7">
+      <c r="G237" s="3">
         <v>196.00000000000006</v>
       </c>
     </row>
@@ -50636,16 +50636,16 @@
       <c r="C238" s="6">
         <v>7200.0000000000055</v>
       </c>
-      <c r="D238" s="7">
+      <c r="D238" s="3">
         <v>20.000000000000014</v>
       </c>
-      <c r="E238" s="7" t="s">
+      <c r="E238" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F238" s="7">
+      <c r="F238" s="3">
         <v>5417.7600000000048</v>
       </c>
-      <c r="G238" s="7">
+      <c r="G238" s="3">
         <v>600.00000000000045</v>
       </c>
     </row>
@@ -50660,16 +50660,16 @@
       <c r="C239" s="6">
         <v>3800</v>
       </c>
-      <c r="D239" s="7">
+      <c r="D239" s="3">
         <v>11</v>
       </c>
-      <c r="E239" s="7" t="s">
+      <c r="E239" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F239" s="7">
+      <c r="F239" s="3">
         <v>2929.9000000000005</v>
       </c>
-      <c r="G239" s="7">
+      <c r="G239" s="3">
         <v>330</v>
       </c>
     </row>
@@ -50684,16 +50684,16 @@
       <c r="C240" s="6">
         <v>5500</v>
       </c>
-      <c r="D240" s="7">
+      <c r="D240" s="3">
         <v>16</v>
       </c>
-      <c r="E240" s="7" t="s">
+      <c r="E240" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F240" s="7">
+      <c r="F240" s="3">
         <v>4221.9000000000005</v>
       </c>
-      <c r="G240" s="7">
+      <c r="G240" s="3">
         <v>480</v>
       </c>
     </row>
@@ -50708,16 +50708,16 @@
       <c r="C241" s="6">
         <v>4308.0000000000018</v>
       </c>
-      <c r="D241" s="7">
+      <c r="D241" s="3">
         <v>12.000000000000005</v>
       </c>
-      <c r="E241" s="7" t="s">
+      <c r="E241" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F241" s="7">
+      <c r="F241" s="3">
         <v>3315.8880000000008</v>
       </c>
-      <c r="G241" s="7">
+      <c r="G241" s="3">
         <v>96.000000000000043</v>
       </c>
     </row>
@@ -50732,16 +50732,16 @@
       <c r="C242" s="6">
         <v>5028.0000000000009</v>
       </c>
-      <c r="D242" s="7">
+      <c r="D242" s="3">
         <v>14.000000000000004</v>
       </c>
-      <c r="E242" s="7" t="s">
+      <c r="E242" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F242" s="7">
+      <c r="F242" s="3">
         <v>3871.1336000000015</v>
       </c>
-      <c r="G242" s="7">
+      <c r="G242" s="3">
         <v>112.00000000000003</v>
       </c>
     </row>
@@ -50756,16 +50756,16 @@
       <c r="C243" s="6">
         <v>7229.0000000000036</v>
       </c>
-      <c r="D243" s="7">
+      <c r="D243" s="3">
         <v>20.000000000000011</v>
       </c>
-      <c r="E243" s="7" t="s">
+      <c r="E243" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F243" s="7">
+      <c r="F243" s="3">
         <v>5630.087300000002</v>
       </c>
-      <c r="G243" s="7">
+      <c r="G243" s="3">
         <v>520.00000000000023</v>
       </c>
     </row>
@@ -50780,16 +50780,16 @@
       <c r="C244" s="6">
         <v>5059.9999999999991</v>
       </c>
-      <c r="D244" s="7">
+      <c r="D244" s="3">
         <v>9.9999999999999982</v>
       </c>
-      <c r="E244" s="7" t="s">
+      <c r="E244" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F244" s="7">
+      <c r="F244" s="3">
         <v>3453.2439999999983</v>
       </c>
-      <c r="G244" s="7">
+      <c r="G244" s="3">
         <v>449.99999999999994</v>
       </c>
     </row>
@@ -50804,16 +50804,16 @@
       <c r="C245" s="6">
         <v>4950</v>
       </c>
-      <c r="D245" s="7">
+      <c r="D245" s="3">
         <v>10</v>
       </c>
-      <c r="E245" s="7" t="s">
+      <c r="E245" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F245" s="7">
+      <c r="F245" s="3">
         <v>3439.395</v>
       </c>
-      <c r="G245" s="7">
+      <c r="G245" s="3">
         <v>450</v>
       </c>
     </row>
@@ -50828,16 +50828,16 @@
       <c r="C246" s="6">
         <v>5580.0000000000018</v>
       </c>
-      <c r="D246" s="7">
+      <c r="D246" s="3">
         <v>12.000000000000004</v>
       </c>
-      <c r="E246" s="7" t="s">
+      <c r="E246" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F246" s="7">
+      <c r="F246" s="3">
         <v>4056.1380000000022</v>
       </c>
-      <c r="G246" s="7">
+      <c r="G246" s="3">
         <v>540.00000000000011</v>
       </c>
     </row>
@@ -50852,16 +50852,16 @@
       <c r="C247" s="6">
         <v>5479.9999999999991</v>
       </c>
-      <c r="D247" s="7">
+      <c r="D247" s="3">
         <v>11.999999999999998</v>
       </c>
-      <c r="E247" s="7" t="s">
+      <c r="E247" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F247" s="7">
+      <c r="F247" s="3">
         <v>4007.1</v>
       </c>
-      <c r="G247" s="7">
+      <c r="G247" s="3">
         <v>539.99999999999989</v>
       </c>
     </row>
@@ -50876,16 +50876,16 @@
       <c r="C248" s="6">
         <v>2255</v>
       </c>
-      <c r="D248" s="7">
+      <c r="D248" s="3">
         <v>5</v>
       </c>
-      <c r="E248" s="7" t="s">
+      <c r="E248" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F248" s="7">
+      <c r="F248" s="3">
         <v>1630.7295000000001</v>
       </c>
-      <c r="G248" s="7">
+      <c r="G248" s="3">
         <v>225</v>
       </c>
     </row>
@@ -50900,16 +50900,16 @@
       <c r="C249" s="6">
         <v>4510</v>
       </c>
-      <c r="D249" s="7">
+      <c r="D249" s="3">
         <v>10</v>
       </c>
-      <c r="E249" s="7" t="s">
+      <c r="E249" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F249" s="7">
+      <c r="F249" s="3">
         <v>3261.4590000000003</v>
       </c>
-      <c r="G249" s="7">
+      <c r="G249" s="3">
         <v>450</v>
       </c>
     </row>
@@ -50924,16 +50924,16 @@
       <c r="C250" s="6">
         <v>8900.0000000000036</v>
       </c>
-      <c r="D250" s="7">
+      <c r="D250" s="3">
         <v>20.000000000000011</v>
       </c>
-      <c r="E250" s="7" t="s">
+      <c r="E250" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F250" s="7">
+      <c r="F250" s="3">
         <v>6072.4600000000028</v>
       </c>
-      <c r="G250" s="7">
+      <c r="G250" s="3">
         <v>1200.0000000000007</v>
       </c>
     </row>
@@ -50948,16 +50948,16 @@
       <c r="C251" s="6">
         <v>5219.9999999999991</v>
       </c>
-      <c r="D251" s="7">
+      <c r="D251" s="3">
         <v>9.9999999999999982</v>
       </c>
-      <c r="E251" s="7" t="s">
+      <c r="E251" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F251" s="7">
+      <c r="F251" s="3">
         <v>3539.5419999999986</v>
       </c>
-      <c r="G251" s="7">
+      <c r="G251" s="3">
         <v>499.99999999999989</v>
       </c>
     </row>
@@ -50972,16 +50972,16 @@
       <c r="C252" s="6">
         <v>5100</v>
       </c>
-      <c r="D252" s="7">
+      <c r="D252" s="3">
         <v>10</v>
       </c>
-      <c r="E252" s="7" t="s">
+      <c r="E252" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F252" s="7">
+      <c r="F252" s="3">
         <v>3660.1800000000007</v>
       </c>
-      <c r="G252" s="7">
+      <c r="G252" s="3">
         <v>450</v>
       </c>
     </row>
@@ -50996,16 +50996,16 @@
       <c r="C253" s="6">
         <v>6060.0000000000018</v>
       </c>
-      <c r="D253" s="7">
+      <c r="D253" s="3">
         <v>12.000000000000004</v>
       </c>
-      <c r="E253" s="7" t="s">
+      <c r="E253" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F253" s="7">
+      <c r="F253" s="3">
         <v>4295.0340000000006</v>
       </c>
-      <c r="G253" s="7">
+      <c r="G253" s="3">
         <v>540.00000000000011</v>
       </c>
     </row>
@@ -51020,16 +51020,16 @@
       <c r="C254" s="6">
         <v>5999.9999999999991</v>
       </c>
-      <c r="D254" s="7">
+      <c r="D254" s="3">
         <v>11.999999999999998</v>
       </c>
-      <c r="E254" s="7" t="s">
+      <c r="E254" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F254" s="7">
+      <c r="F254" s="3">
         <v>4254.5999999999985</v>
       </c>
-      <c r="G254" s="7">
+      <c r="G254" s="3">
         <v>479.99999999999994</v>
       </c>
     </row>
@@ -51044,16 +51044,16 @@
       <c r="C255" s="6">
         <v>9200.0000000000036</v>
       </c>
-      <c r="D255" s="7">
+      <c r="D255" s="3">
         <v>20.000000000000011</v>
       </c>
-      <c r="E255" s="7" t="s">
+      <c r="E255" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F255" s="7">
+      <c r="F255" s="3">
         <v>6850.9200000000028</v>
       </c>
-      <c r="G255" s="7">
+      <c r="G255" s="3">
         <v>900.00000000000045</v>
       </c>
     </row>
@@ -51068,16 +51068,16 @@
       <c r="C256" s="6">
         <v>9500.0000000000036</v>
       </c>
-      <c r="D256" s="7">
+      <c r="D256" s="3">
         <v>20.000000000000011</v>
       </c>
-      <c r="E256" s="7" t="s">
+      <c r="E256" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F256" s="7">
+      <c r="F256" s="3">
         <v>7801.4000000000033</v>
       </c>
-      <c r="G256" s="7">
+      <c r="G256" s="3">
         <v>0</v>
       </c>
     </row>
@@ -51092,16 +51092,16 @@
       <c r="C257" s="6">
         <v>5759.9999999999991</v>
       </c>
-      <c r="D257" s="7">
+      <c r="D257" s="3">
         <v>9.9999999999999982</v>
       </c>
-      <c r="E257" s="7" t="s">
+      <c r="E257" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F257" s="7">
+      <c r="F257" s="3">
         <v>3642.3679999999995</v>
       </c>
-      <c r="G257" s="7">
+      <c r="G257" s="3">
         <v>399.99999999999994</v>
       </c>
     </row>
@@ -51116,16 +51116,16 @@
       <c r="C258" s="6">
         <v>5650</v>
       </c>
-      <c r="D258" s="7">
+      <c r="D258" s="3">
         <v>10</v>
       </c>
-      <c r="E258" s="7" t="s">
+      <c r="E258" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F258" s="7">
+      <c r="F258" s="3">
         <v>4266.8799999999992</v>
       </c>
-      <c r="G258" s="7">
+      <c r="G258" s="3">
         <v>0</v>
       </c>
     </row>
@@ -51140,16 +51140,16 @@
       <c r="C259" s="6">
         <v>6900.0000000000018</v>
       </c>
-      <c r="D259" s="7">
+      <c r="D259" s="3">
         <v>12.000000000000004</v>
       </c>
-      <c r="E259" s="7" t="s">
+      <c r="E259" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F259" s="7">
+      <c r="F259" s="3">
         <v>4465.0800000000017</v>
       </c>
-      <c r="G259" s="7">
+      <c r="G259" s="3">
         <v>480.00000000000011</v>
       </c>
     </row>
@@ -51164,16 +51164,16 @@
       <c r="C260" s="6">
         <v>6799.9999999999991</v>
       </c>
-      <c r="D260" s="7">
+      <c r="D260" s="3">
         <v>11.999999999999998</v>
       </c>
-      <c r="E260" s="7" t="s">
+      <c r="E260" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F260" s="7">
+      <c r="F260" s="3">
         <v>4428.2</v>
       </c>
-      <c r="G260" s="7">
+      <c r="G260" s="3">
         <v>479.99999999999994</v>
       </c>
     </row>
@@ -51188,16 +51188,16 @@
       <c r="C261" s="6">
         <v>5600</v>
       </c>
-      <c r="D261" s="7">
+      <c r="D261" s="3">
         <v>10</v>
       </c>
-      <c r="E261" s="7" t="s">
+      <c r="E261" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F261" s="7">
+      <c r="F261" s="3">
         <v>3646.8</v>
       </c>
-      <c r="G261" s="7">
+      <c r="G261" s="3">
         <v>400</v>
       </c>
     </row>
@@ -51212,16 +51212,16 @@
       <c r="C262" s="6">
         <v>10800.000000000005</v>
       </c>
-      <c r="D262" s="7">
+      <c r="D262" s="3">
         <v>20.000000000000011</v>
       </c>
-      <c r="E262" s="7" t="s">
+      <c r="E262" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F262" s="7">
+      <c r="F262" s="3">
         <v>7079.3200000000043</v>
       </c>
-      <c r="G262" s="7">
+      <c r="G262" s="3">
         <v>800.00000000000045</v>
       </c>
     </row>
@@ -51236,16 +51236,16 @@
       <c r="C263" s="6">
         <v>3865</v>
       </c>
-      <c r="D263" s="7">
+      <c r="D263" s="3">
         <v>7</v>
       </c>
-      <c r="E263" s="7" t="s">
+      <c r="E263" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F263" s="7">
+      <c r="F263" s="3">
         <v>2523.1295000000005</v>
       </c>
-      <c r="G263" s="7">
+      <c r="G263" s="3">
         <v>280</v>
       </c>
     </row>
@@ -51260,16 +51260,16 @@
       <c r="C264" s="6">
         <v>5450</v>
       </c>
-      <c r="D264" s="7">
+      <c r="D264" s="3">
         <v>10</v>
       </c>
-      <c r="E264" s="7" t="s">
+      <c r="E264" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F264" s="7">
+      <c r="F264" s="3">
         <v>3576.2600000000007</v>
       </c>
-      <c r="G264" s="7">
+      <c r="G264" s="3">
         <v>400</v>
       </c>
     </row>
@@ -51284,16 +51284,16 @@
       <c r="C265" s="6">
         <v>2175</v>
       </c>
-      <c r="D265" s="7">
+      <c r="D265" s="3">
         <v>5</v>
       </c>
-      <c r="E265" s="7" t="s">
+      <c r="E265" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F265" s="7">
+      <c r="F265" s="3">
         <v>1941.405</v>
       </c>
-      <c r="G265" s="7">
+      <c r="G265" s="3">
         <v>0</v>
       </c>
     </row>
@@ -51308,16 +51308,16 @@
       <c r="C266" s="6">
         <v>8540.0000000000036</v>
       </c>
-      <c r="D266" s="7">
+      <c r="D266" s="3">
         <v>20.000000000000011</v>
       </c>
-      <c r="E266" s="7" t="s">
+      <c r="E266" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F266" s="7">
+      <c r="F266" s="3">
         <v>7622.8040000000037</v>
       </c>
-      <c r="G266" s="7">
+      <c r="G266" s="3">
         <v>0</v>
       </c>
     </row>
@@ -51332,16 +51332,16 @@
       <c r="C267" s="6">
         <v>5859.9999999999991</v>
       </c>
-      <c r="D267" s="7">
+      <c r="D267" s="3">
         <v>9.9999999999999982</v>
       </c>
-      <c r="E267" s="7" t="s">
+      <c r="E267" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F267" s="7">
+      <c r="F267" s="3">
         <v>4319.9919999999993</v>
       </c>
-      <c r="G267" s="7">
+      <c r="G267" s="3">
         <v>0</v>
       </c>
     </row>
@@ -51356,16 +51356,16 @@
       <c r="C268" s="6">
         <v>5800</v>
       </c>
-      <c r="D268" s="7">
+      <c r="D268" s="3">
         <v>10</v>
       </c>
-      <c r="E268" s="7" t="s">
+      <c r="E268" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F268" s="7">
+      <c r="F268" s="3">
         <v>3670.1</v>
       </c>
-      <c r="G268" s="7">
+      <c r="G268" s="3">
         <v>500</v>
       </c>
     </row>
@@ -51380,16 +51380,16 @@
       <c r="C269" s="6">
         <v>6480.0000000000018</v>
       </c>
-      <c r="D269" s="7">
+      <c r="D269" s="3">
         <v>12.000000000000004</v>
       </c>
-      <c r="E269" s="7" t="s">
+      <c r="E269" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F269" s="7">
+      <c r="F269" s="3">
         <v>4764.7440000000006</v>
       </c>
-      <c r="G269" s="7">
+      <c r="G269" s="3">
         <v>0</v>
       </c>
     </row>
@@ -51404,16 +51404,16 @@
       <c r="C270" s="6">
         <v>6419.9999999999991</v>
       </c>
-      <c r="D270" s="7">
+      <c r="D270" s="3">
         <v>11.999999999999998</v>
       </c>
-      <c r="E270" s="7" t="s">
+      <c r="E270" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F270" s="7">
+      <c r="F270" s="3">
         <v>4728.33</v>
       </c>
-      <c r="G270" s="7">
+      <c r="G270" s="3">
         <v>0</v>
       </c>
     </row>
@@ -51428,16 +51428,16 @@
       <c r="C271" s="6">
         <v>2800</v>
       </c>
-      <c r="D271" s="7">
+      <c r="D271" s="3">
         <v>5</v>
       </c>
-      <c r="E271" s="7" t="s">
+      <c r="E271" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F271" s="7">
+      <c r="F271" s="3">
         <v>2070.6</v>
       </c>
-      <c r="G271" s="7">
+      <c r="G271" s="3">
         <v>0</v>
       </c>
     </row>
@@ -51452,16 +51452,16 @@
       <c r="C272" s="6">
         <v>10800.000000000005</v>
       </c>
-      <c r="D272" s="7">
+      <c r="D272" s="3">
         <v>20.000000000000011</v>
       </c>
-      <c r="E272" s="7" t="s">
+      <c r="E272" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F272" s="7">
+      <c r="F272" s="3">
         <v>8003.8800000000037</v>
       </c>
-      <c r="G272" s="7">
+      <c r="G272" s="3">
         <v>0</v>
       </c>
     </row>
@@ -51476,16 +51476,16 @@
       <c r="C273" s="6">
         <v>3885</v>
       </c>
-      <c r="D273" s="7">
+      <c r="D273" s="3">
         <v>7</v>
       </c>
-      <c r="E273" s="7" t="s">
+      <c r="E273" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F273" s="7">
+      <c r="F273" s="3">
         <v>2884.6125000000002</v>
       </c>
-      <c r="G273" s="7">
+      <c r="G273" s="3">
         <v>0</v>
       </c>
     </row>
@@ -51500,1810 +51500,1833 @@
       <c r="C274" s="6">
         <v>5500</v>
       </c>
-      <c r="D274" s="7">
+      <c r="D274" s="3">
         <v>10</v>
       </c>
-      <c r="E274" s="7" t="s">
+      <c r="E274" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F274" s="7">
+      <c r="F274" s="3">
         <v>4090.9</v>
       </c>
-      <c r="G274" s="7">
+      <c r="G274" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A275" s="8">
+      <c r="A275" s="2">
         <v>7403401</v>
       </c>
-      <c r="B275" s="8" t="s">
+      <c r="B275" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C275" s="6">
         <v>0</v>
       </c>
-      <c r="D275" s="7">
+      <c r="D275" s="3">
         <v>210</v>
       </c>
-      <c r="E275" s="7" t="s">
+      <c r="E275" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F275" s="7">
+      <c r="F275" s="3">
         <v>39648</v>
       </c>
-      <c r="G275" s="7">
+      <c r="G275" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A276" s="8">
+      <c r="A276" s="2">
         <v>2960401</v>
       </c>
-      <c r="B276" s="8" t="s">
+      <c r="B276" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C276" s="6">
         <v>0</v>
       </c>
-      <c r="D276" s="7">
+      <c r="D276" s="3">
         <v>210</v>
       </c>
-      <c r="E276" s="7" t="s">
+      <c r="E276" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F276" s="7">
+      <c r="F276" s="3">
         <v>157353</v>
       </c>
-      <c r="G276" s="7">
+      <c r="G276" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A277" s="8">
+      <c r="A277" s="2">
         <v>7427401</v>
       </c>
-      <c r="B277" s="8" t="s">
+      <c r="B277" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C277" s="6">
         <v>0</v>
       </c>
-      <c r="D277" s="7">
+      <c r="D277" s="3">
         <v>210</v>
       </c>
-      <c r="E277" s="7" t="s">
+      <c r="E277" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F277" s="7">
-        <v>80535</v>
-      </c>
-      <c r="G277" s="7">
+      <c r="F277">
+        <v>68250</v>
+      </c>
+      <c r="G277" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A278" s="8">
+      <c r="A278" s="2">
         <v>7428401</v>
       </c>
-      <c r="B278" s="8" t="s">
+      <c r="B278" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C278" s="6">
         <v>0</v>
       </c>
-      <c r="D278" s="7">
+      <c r="D278" s="3">
         <v>210</v>
       </c>
-      <c r="E278" s="7" t="s">
+      <c r="E278" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F278" s="7">
+      <c r="F278" s="3">
         <v>88712.4</v>
       </c>
-      <c r="G278" s="7">
+      <c r="G278" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A279" s="8">
+      <c r="A279" s="2">
         <v>7670401</v>
       </c>
-      <c r="B279" s="8" t="s">
+      <c r="B279" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C279" s="6">
         <v>0</v>
       </c>
-      <c r="D279" s="7">
+      <c r="D279" s="3">
         <v>210</v>
       </c>
-      <c r="E279" s="7" t="s">
+      <c r="E279" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F279" s="7">
+      <c r="F279" s="3">
         <v>60710.999999999993</v>
       </c>
-      <c r="G279" s="7">
+      <c r="G279" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A280" s="8">
+      <c r="A280" s="2">
         <v>7688401</v>
       </c>
-      <c r="B280" s="8" t="s">
+      <c r="B280" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C280" s="6">
         <v>0</v>
       </c>
-      <c r="D280" s="7">
+      <c r="D280" s="3">
         <v>210</v>
       </c>
-      <c r="E280" s="7" t="s">
+      <c r="E280" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F280" s="7">
+      <c r="F280" s="3">
         <v>63932.4</v>
       </c>
-      <c r="G280" s="7">
+      <c r="G280" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A281" s="8">
+      <c r="A281" s="2">
         <v>2968401</v>
       </c>
-      <c r="B281" s="8" t="s">
+      <c r="B281" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C281" s="6">
         <v>0</v>
       </c>
-      <c r="D281" s="7">
+      <c r="D281" s="3">
         <v>210</v>
       </c>
-      <c r="E281" s="7" t="s">
+      <c r="E281" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F281" s="7">
+      <c r="F281" s="3">
         <v>64428</v>
       </c>
-      <c r="G281" s="7">
+      <c r="G281" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A282" s="8">
+      <c r="A282" s="2">
         <v>7205401</v>
       </c>
-      <c r="B282" s="8" t="s">
+      <c r="B282" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C282" s="6">
         <v>0</v>
       </c>
-      <c r="D282" s="7">
+      <c r="D282" s="3">
         <v>210</v>
       </c>
-      <c r="E282" s="7" t="s">
+      <c r="E282" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F282" s="7">
+      <c r="F282" s="3">
         <v>85491</v>
       </c>
-      <c r="G282" s="7">
+      <c r="G282" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A283" s="8">
+      <c r="A283" s="2">
         <v>7420401</v>
       </c>
-      <c r="B283" s="8" t="s">
+      <c r="B283" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C283" s="6">
         <v>0</v>
       </c>
-      <c r="D283" s="7">
+      <c r="D283" s="3">
         <v>210</v>
       </c>
-      <c r="E283" s="7" t="s">
+      <c r="E283" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F283" s="7">
+      <c r="F283" s="3">
         <v>79791.599999999991</v>
       </c>
-      <c r="G283" s="7">
+      <c r="G283" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A284" s="8">
+      <c r="A284" s="2">
         <v>7421401</v>
       </c>
-      <c r="B284" s="8" t="s">
+      <c r="B284" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C284" s="6">
         <v>0</v>
       </c>
-      <c r="D284" s="7">
+      <c r="D284" s="3">
         <v>210</v>
       </c>
-      <c r="E284" s="7" t="s">
+      <c r="E284" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F284" s="7">
+      <c r="F284" s="3">
         <v>90199.2</v>
       </c>
-      <c r="G284" s="7">
+      <c r="G284" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A285" s="8">
+      <c r="A285" s="2">
         <v>7477401</v>
       </c>
-      <c r="B285" s="8" t="s">
+      <c r="B285" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C285" s="6">
         <v>0</v>
       </c>
-      <c r="D285" s="7">
+      <c r="D285" s="3">
         <v>210</v>
       </c>
-      <c r="E285" s="7" t="s">
+      <c r="E285" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F285" s="7">
+      <c r="F285" s="3">
         <v>66658.2</v>
       </c>
-      <c r="G285" s="7">
+      <c r="G285" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A286" s="8">
+      <c r="A286" s="2">
         <v>7209401</v>
       </c>
-      <c r="B286" s="8" t="s">
+      <c r="B286" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C286" s="6">
         <v>0</v>
       </c>
-      <c r="D286" s="7">
+      <c r="D286" s="3">
         <v>50</v>
       </c>
-      <c r="E286" s="7" t="s">
+      <c r="E286" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F286" s="7">
+      <c r="F286" s="3">
         <v>193036.19999999998</v>
       </c>
-      <c r="G286" s="7">
+      <c r="G286" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A287" s="8">
+      <c r="A287" s="2">
         <v>7202271</v>
       </c>
-      <c r="B287" s="8" t="s">
+      <c r="B287" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C287" s="6">
         <v>0</v>
       </c>
-      <c r="D287" s="7">
+      <c r="D287" s="3">
         <v>50</v>
       </c>
-      <c r="E287" s="7" t="s">
+      <c r="E287" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F287" s="7">
+      <c r="F287" s="3">
         <v>18142.5</v>
       </c>
-      <c r="G287" s="7">
+      <c r="G287" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A288" s="8">
+      <c r="A288" s="2">
         <v>7206271</v>
       </c>
-      <c r="B288" s="8" t="s">
+      <c r="B288" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C288" s="6">
         <v>0</v>
       </c>
-      <c r="D288" s="7">
+      <c r="D288" s="3">
         <v>50</v>
       </c>
-      <c r="E288" s="7" t="s">
+      <c r="E288" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F288" s="7">
+      <c r="F288" s="3">
         <v>17098.2</v>
       </c>
-      <c r="G288" s="7">
+      <c r="G288" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A289" s="8">
+      <c r="A289" s="2">
         <v>7207271</v>
       </c>
-      <c r="B289" s="8" t="s">
+      <c r="B289" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C289" s="6">
         <v>0</v>
       </c>
-      <c r="D289" s="7">
+      <c r="D289" s="3">
         <v>50</v>
       </c>
-      <c r="E289" s="7" t="s">
+      <c r="E289" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F289" s="7">
+      <c r="F289" s="3">
         <v>15558.3</v>
       </c>
-      <c r="G289" s="7">
+      <c r="G289" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A290" s="8">
+      <c r="A290" s="2">
         <v>7208271</v>
       </c>
-      <c r="B290" s="8" t="s">
+      <c r="B290" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C290" s="6">
         <v>0</v>
       </c>
-      <c r="D290" s="7">
+      <c r="D290" s="3">
         <v>210</v>
       </c>
-      <c r="E290" s="7" t="s">
+      <c r="E290" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F290" s="7">
+      <c r="F290" s="3">
         <v>16756</v>
       </c>
-      <c r="G290" s="7">
+      <c r="G290" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A291" s="8">
+      <c r="A291" s="2">
         <v>7202401</v>
       </c>
-      <c r="B291" s="8" t="s">
+      <c r="B291" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C291" s="6">
         <v>0</v>
       </c>
-      <c r="D291" s="7">
+      <c r="D291" s="3">
         <v>210</v>
       </c>
-      <c r="E291" s="7" t="s">
+      <c r="E291" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F291" s="7">
+      <c r="F291" s="3">
         <v>76198.5</v>
       </c>
-      <c r="G291" s="7">
+      <c r="G291" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A292" s="8">
+      <c r="A292" s="2">
         <v>7206401</v>
       </c>
-      <c r="B292" s="8" t="s">
+      <c r="B292" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C292" s="6">
         <v>0</v>
       </c>
-      <c r="D292" s="7">
+      <c r="D292" s="3">
         <v>210</v>
       </c>
-      <c r="E292" s="7" t="s">
+      <c r="E292" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F292" s="7">
+      <c r="F292" s="3">
         <v>71812.44</v>
       </c>
-      <c r="G292" s="7">
+      <c r="G292" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A293" s="8">
+      <c r="A293" s="2">
         <v>7207401</v>
       </c>
-      <c r="B293" s="8" t="s">
+      <c r="B293" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C293" s="6">
         <v>0</v>
       </c>
-      <c r="D293" s="7">
+      <c r="D293" s="3">
         <v>210</v>
       </c>
-      <c r="E293" s="7" t="s">
+      <c r="E293" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F293" s="7">
+      <c r="F293" s="3">
         <v>65344.86</v>
       </c>
-      <c r="G293" s="7">
+      <c r="G293" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A294" s="8">
+      <c r="A294" s="2">
         <v>7208401</v>
       </c>
-      <c r="B294" s="8" t="s">
+      <c r="B294" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C294" s="6">
         <v>0</v>
       </c>
-      <c r="D294" s="7">
+      <c r="D294" s="3">
         <v>210</v>
       </c>
-      <c r="E294" s="7" t="s">
+      <c r="E294" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F294" s="7">
+      <c r="F294" s="3">
         <v>70375.199999999997</v>
       </c>
-      <c r="G294" s="7">
+      <c r="G294" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A295" s="8">
+      <c r="A295" s="2">
         <v>7264401</v>
       </c>
-      <c r="B295" s="8" t="s">
+      <c r="B295" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C295" s="6">
         <v>0</v>
       </c>
-      <c r="D295" s="7">
+      <c r="D295" s="3">
         <v>210</v>
       </c>
-      <c r="E295" s="7" t="s">
+      <c r="E295" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F295" s="7">
+      <c r="F295" s="3">
         <v>75331.199999999997</v>
       </c>
-      <c r="G295" s="7">
+      <c r="G295" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A296" s="8">
+      <c r="A296" s="2">
         <v>7267401</v>
       </c>
-      <c r="B296" s="8" t="s">
+      <c r="B296" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C296" s="6">
         <v>0</v>
       </c>
-      <c r="D296" s="7">
+      <c r="D296" s="3">
         <v>210</v>
       </c>
-      <c r="E296" s="7" t="s">
+      <c r="E296" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F296" s="7">
+      <c r="F296" s="3">
         <v>171725.4</v>
       </c>
-      <c r="G296" s="7">
+      <c r="G296" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A297" s="8">
+      <c r="A297" s="2">
         <v>7265401</v>
       </c>
-      <c r="B297" s="8" t="s">
+      <c r="B297" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C297" s="6">
         <v>0</v>
       </c>
-      <c r="D297" s="7">
+      <c r="D297" s="3">
         <v>210</v>
       </c>
-      <c r="E297" s="7" t="s">
+      <c r="E297" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F297" s="7">
+      <c r="F297" s="3">
         <v>109775.40000000001</v>
       </c>
-      <c r="G297" s="7">
+      <c r="G297" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A298" s="8">
+      <c r="A298" s="2">
         <v>1301401</v>
       </c>
-      <c r="B298" s="8" t="s">
+      <c r="B298" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C298" s="6">
         <v>0</v>
       </c>
-      <c r="D298" s="7">
+      <c r="D298" s="3">
         <v>210</v>
       </c>
-      <c r="E298" s="7" t="s">
+      <c r="E298" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F298" s="7">
+      <c r="F298" s="3">
         <v>56498.399999999994</v>
       </c>
-      <c r="G298" s="7">
+      <c r="G298" s="3">
         <v>630</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A299" s="8">
+      <c r="A299" s="2">
         <v>1404401</v>
       </c>
-      <c r="B299" s="8" t="s">
+      <c r="B299" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C299" s="6">
         <v>0</v>
       </c>
-      <c r="D299" s="7">
+      <c r="D299" s="3">
         <v>210</v>
       </c>
-      <c r="E299" s="7" t="s">
+      <c r="E299" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F299" s="7">
+      <c r="F299" s="3">
         <v>65667</v>
       </c>
-      <c r="G299" s="7">
+      <c r="G299" s="3">
         <v>630</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A300" s="8">
+      <c r="A300" s="2">
         <v>7436401</v>
       </c>
-      <c r="B300" s="8" t="s">
+      <c r="B300" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C300" s="6">
         <v>0</v>
       </c>
-      <c r="D300" s="7">
+      <c r="D300" s="3">
         <v>210</v>
       </c>
-      <c r="E300" s="7" t="s">
+      <c r="E300" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F300" s="7">
+      <c r="F300" s="3">
         <v>69631.8</v>
       </c>
-      <c r="G300" s="7">
+      <c r="G300" s="3">
         <v>2940</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A301" s="8">
+      <c r="A301" s="2">
         <v>7470401</v>
       </c>
-      <c r="B301" s="8" t="s">
+      <c r="B301" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C301" s="6">
         <v>0</v>
       </c>
-      <c r="D301" s="7">
+      <c r="D301" s="3">
         <v>210</v>
       </c>
-      <c r="E301" s="7" t="s">
+      <c r="E301" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F301" s="7">
+      <c r="F301" s="3">
         <v>56993.999999999993</v>
       </c>
-      <c r="G301" s="7">
+      <c r="G301" s="3">
         <v>1890</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A302" s="8">
+      <c r="A302" s="2">
         <v>7472401</v>
       </c>
-      <c r="B302" s="8" t="s">
+      <c r="B302" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C302" s="6">
         <v>0</v>
       </c>
-      <c r="D302" s="7">
+      <c r="D302" s="3">
         <v>210</v>
       </c>
-      <c r="E302" s="7" t="s">
+      <c r="E302" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F302" s="7">
+      <c r="F302" s="3">
         <v>57241.799999999996</v>
       </c>
-      <c r="G302" s="7">
+      <c r="G302" s="3">
         <v>840</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A303" s="8">
+      <c r="A303" s="2">
         <v>7485401</v>
       </c>
-      <c r="B303" s="8" t="s">
+      <c r="B303" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C303" s="6">
         <v>0</v>
       </c>
-      <c r="D303" s="7">
+      <c r="D303" s="3">
         <v>50</v>
       </c>
-      <c r="E303" s="7" t="s">
+      <c r="E303" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F303" s="7">
+      <c r="F303" s="3">
         <v>54020.4</v>
       </c>
-      <c r="G303" s="7">
+      <c r="G303" s="3">
         <v>2940</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A304" s="8">
+      <c r="A304" s="2">
         <v>7489271</v>
       </c>
-      <c r="B304" s="8" t="s">
+      <c r="B304" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C304" s="6">
         <v>0</v>
       </c>
-      <c r="D304" s="7">
+      <c r="D304" s="3">
         <v>210</v>
       </c>
-      <c r="E304" s="7" t="s">
+      <c r="E304" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F304" s="7">
+      <c r="F304" s="3">
         <v>16047.999999999998</v>
       </c>
-      <c r="G304" s="7">
+      <c r="G304" s="3">
         <v>950</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A305" s="8">
+      <c r="A305" s="2">
         <v>7489401</v>
       </c>
-      <c r="B305" s="8" t="s">
+      <c r="B305" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C305" s="6">
         <v>0</v>
       </c>
-      <c r="D305" s="7">
+      <c r="D305" s="3">
         <v>210</v>
       </c>
-      <c r="E305" s="7" t="s">
+      <c r="E305" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F305" s="7">
+      <c r="F305" s="3">
         <v>66906</v>
       </c>
-      <c r="G305" s="7">
+      <c r="G305" s="3">
         <v>3990</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A306" s="8">
+      <c r="A306" s="2">
         <v>7494401</v>
       </c>
-      <c r="B306" s="8" t="s">
+      <c r="B306" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C306" s="6">
         <v>0</v>
       </c>
-      <c r="D306" s="7">
+      <c r="D306" s="3">
         <v>50</v>
       </c>
-      <c r="E306" s="7" t="s">
+      <c r="E306" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F306" s="7">
+      <c r="F306" s="3">
         <v>62941.2</v>
       </c>
-      <c r="G306" s="7">
+      <c r="G306" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A307" s="8">
+      <c r="A307" s="2">
         <v>7577271</v>
       </c>
-      <c r="B307" s="8" t="s">
+      <c r="B307" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C307" s="6">
         <v>0</v>
       </c>
-      <c r="D307" s="7">
+      <c r="D307" s="3">
         <v>210</v>
       </c>
-      <c r="E307" s="7" t="s">
+      <c r="E307" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F307" s="7">
+      <c r="F307" s="3">
         <v>14395.999999999998</v>
       </c>
-      <c r="G307" s="7">
+      <c r="G307" s="3">
         <v>700</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A308" s="8">
+      <c r="A308" s="2">
         <v>7577401</v>
       </c>
-      <c r="B308" s="8" t="s">
+      <c r="B308" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C308" s="6">
         <v>0</v>
       </c>
-      <c r="D308" s="7">
+      <c r="D308" s="3">
         <v>210</v>
       </c>
-      <c r="E308" s="7" t="s">
+      <c r="E308" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F308" s="7">
+      <c r="F308" s="3">
         <v>59967.6</v>
       </c>
-      <c r="G308" s="7">
+      <c r="G308" s="3">
         <v>3150</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A309" s="8">
+      <c r="A309" s="2">
         <v>7612401</v>
       </c>
-      <c r="B309" s="8" t="s">
+      <c r="B309" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C309" s="6">
         <v>0</v>
       </c>
-      <c r="D309" s="7">
+      <c r="D309" s="3">
         <v>210</v>
       </c>
-      <c r="E309" s="7" t="s">
+      <c r="E309" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F309" s="7">
+      <c r="F309" s="3">
         <v>60710.999999999993</v>
       </c>
-      <c r="G309" s="7">
+      <c r="G309" s="3">
         <v>3990</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A310" s="8">
+      <c r="A310" s="2">
         <v>2502401</v>
       </c>
-      <c r="B310" s="8" t="s">
+      <c r="B310" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C310" s="6">
         <v>0</v>
       </c>
-      <c r="D310" s="7">
+      <c r="D310" s="3">
         <v>210</v>
       </c>
-      <c r="E310" s="7" t="s">
+      <c r="E310" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F310" s="7">
+      <c r="F310" s="3">
         <v>61950</v>
       </c>
-      <c r="G310" s="7">
+      <c r="G310" s="3">
         <v>3990</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A311" s="8">
+      <c r="A311" s="2">
         <v>2503401</v>
       </c>
-      <c r="B311" s="8" t="s">
+      <c r="B311" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C311" s="6">
         <v>0</v>
       </c>
-      <c r="D311" s="7">
+      <c r="D311" s="3">
         <v>210</v>
       </c>
-      <c r="E311" s="7" t="s">
+      <c r="E311" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F311" s="7">
+      <c r="F311" s="3">
         <v>67153.799999999988</v>
       </c>
-      <c r="G311" s="7">
+      <c r="G311" s="3">
         <v>2940</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A312" s="8">
+      <c r="A312" s="2">
         <v>4906401</v>
       </c>
-      <c r="B312" s="8" t="s">
+      <c r="B312" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C312" s="6">
         <v>0</v>
       </c>
-      <c r="D312" s="7">
+      <c r="D312" s="3">
         <v>210</v>
       </c>
-      <c r="E312" s="7" t="s">
+      <c r="E312" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F312" s="7">
+      <c r="F312" s="3">
         <v>54268.19999999999</v>
       </c>
-      <c r="G312" s="7">
+      <c r="G312" s="3">
         <v>1890</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A313" s="8">
+      <c r="A313" s="2">
         <v>4925401</v>
       </c>
-      <c r="B313" s="8" t="s">
+      <c r="B313" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C313" s="6">
         <v>0</v>
       </c>
-      <c r="D313" s="7">
+      <c r="D313" s="3">
         <v>210</v>
       </c>
-      <c r="E313" s="7" t="s">
+      <c r="E313" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F313" s="7">
+      <c r="F313" s="3">
         <v>58233</v>
       </c>
-      <c r="G313" s="7">
+      <c r="G313" s="3">
         <v>1050</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A314" s="8">
+      <c r="A314" s="2">
         <v>7511401</v>
       </c>
-      <c r="B314" s="8" t="s">
+      <c r="B314" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C314" s="6">
         <v>0</v>
       </c>
-      <c r="D314" s="7">
+      <c r="D314" s="3">
         <v>210</v>
       </c>
-      <c r="E314" s="7" t="s">
+      <c r="E314" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F314" s="7">
+      <c r="F314" s="3">
         <v>64180.200000000004</v>
       </c>
-      <c r="G314" s="7">
+      <c r="G314" s="3">
         <v>3990</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A315" s="8">
+      <c r="A315" s="2">
         <v>7515401</v>
       </c>
-      <c r="B315" s="8" t="s">
+      <c r="B315" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C315" s="6">
         <v>0</v>
       </c>
-      <c r="D315" s="7">
+      <c r="D315" s="3">
         <v>26</v>
       </c>
-      <c r="E315" s="7" t="s">
+      <c r="E315" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F315" s="7">
+      <c r="F315" s="3">
         <v>66162.600000000006</v>
       </c>
-      <c r="G315" s="7">
+      <c r="G315" s="3">
         <v>5040</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A316" s="8">
+      <c r="A316" s="2">
         <v>4950288</v>
       </c>
-      <c r="B316" s="8" t="s">
+      <c r="B316" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C316" s="6">
         <v>0</v>
       </c>
-      <c r="D316" s="7">
+      <c r="D316" s="3">
         <v>210</v>
       </c>
-      <c r="E316" s="7" t="s">
+      <c r="E316" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F316" s="7">
+      <c r="F316" s="3">
         <v>6688.24</v>
       </c>
-      <c r="G316" s="7">
+      <c r="G316" s="3">
         <v>884</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A317" s="8">
+      <c r="A317" s="2">
         <v>4950401</v>
       </c>
-      <c r="B317" s="8" t="s">
+      <c r="B317" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C317" s="6">
         <v>0</v>
       </c>
-      <c r="D317" s="7">
+      <c r="D317" s="3">
         <v>210</v>
       </c>
-      <c r="E317" s="7" t="s">
+      <c r="E317" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F317" s="7">
+      <c r="F317" s="3">
         <v>58976.399999999994</v>
       </c>
-      <c r="G317" s="7">
+      <c r="G317" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A318" s="8">
+      <c r="A318" s="2">
         <v>7651401</v>
       </c>
-      <c r="B318" s="8" t="s">
+      <c r="B318" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C318" s="6">
         <v>0</v>
       </c>
-      <c r="D318" s="7">
+      <c r="D318" s="3">
         <v>210</v>
       </c>
-      <c r="E318" s="7" t="s">
+      <c r="E318" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F318" s="7">
+      <c r="F318" s="3">
         <v>49064.399999999994</v>
       </c>
-      <c r="G318" s="7">
+      <c r="G318" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A319" s="8">
+      <c r="A319" s="2">
         <v>2900401</v>
       </c>
-      <c r="B319" s="8" t="s">
+      <c r="B319" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C319" s="6">
         <v>0</v>
       </c>
-      <c r="D319" s="7">
+      <c r="D319" s="3">
         <v>210</v>
       </c>
-      <c r="E319" s="7" t="s">
+      <c r="E319" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F319" s="7">
+      <c r="F319" s="3">
         <v>69131.243999999992</v>
       </c>
-      <c r="G319" s="7">
+      <c r="G319" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A320" s="8">
+      <c r="A320" s="2">
         <v>2900403</v>
       </c>
-      <c r="B320" s="8" t="s">
+      <c r="B320" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C320" s="6">
         <v>0</v>
       </c>
-      <c r="D320" s="7">
+      <c r="D320" s="3">
         <v>182</v>
       </c>
-      <c r="E320" s="7" t="s">
+      <c r="E320" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F320" s="7">
+      <c r="F320" s="3">
         <v>69131.243999999992</v>
       </c>
-      <c r="G320" s="7">
+      <c r="G320" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A321" s="8">
+      <c r="A321" s="2">
         <v>7701451</v>
       </c>
-      <c r="B321" s="8" t="s">
+      <c r="B321" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C321" s="6">
         <v>0</v>
       </c>
-      <c r="D321" s="7">
+      <c r="D321" s="3">
         <v>182</v>
       </c>
-      <c r="E321" s="7" t="s">
+      <c r="E321" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F321" s="7">
+      <c r="F321" s="3">
         <v>58844.24</v>
       </c>
-      <c r="G321" s="7">
+      <c r="G321" s="3">
         <v>4732</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A322" s="8">
+      <c r="A322" s="2">
         <v>7705451</v>
       </c>
-      <c r="B322" s="8" t="s">
+      <c r="B322" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C322" s="6">
         <v>0</v>
       </c>
-      <c r="D322" s="7">
+      <c r="D322" s="3">
         <v>182</v>
       </c>
-      <c r="E322" s="7" t="s">
+      <c r="E322" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F322" s="7">
+      <c r="F322" s="3">
         <v>59059</v>
       </c>
-      <c r="G322" s="7">
+      <c r="G322" s="3">
         <v>6370</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A323" s="8">
+      <c r="A323" s="2">
         <v>7727451</v>
       </c>
-      <c r="B323" s="8" t="s">
+      <c r="B323" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C323" s="6">
         <v>0</v>
       </c>
-      <c r="D323" s="7">
+      <c r="D323" s="3">
         <v>182</v>
       </c>
-      <c r="E323" s="7" t="s">
+      <c r="E323" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F323" s="7">
+      <c r="F323" s="3">
         <v>76239.8</v>
       </c>
-      <c r="G323" s="7">
+      <c r="G323" s="3">
         <v>10010</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A324" s="8">
+      <c r="A324" s="2">
         <v>7849451</v>
       </c>
-      <c r="B324" s="8" t="s">
+      <c r="B324" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C324" s="6">
         <v>0</v>
       </c>
-      <c r="D324" s="7">
+      <c r="D324" s="3">
         <v>182</v>
       </c>
-      <c r="E324" s="7" t="s">
+      <c r="E324" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F324" s="7">
+      <c r="F324" s="3">
         <v>79890.720000000001</v>
       </c>
-      <c r="G324" s="7">
+      <c r="G324" s="3">
         <v>4186</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A325" s="8">
+      <c r="A325" s="2">
         <v>7903451</v>
       </c>
-      <c r="B325" s="8" t="s">
+      <c r="B325" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C325" s="6">
         <v>0</v>
       </c>
-      <c r="D325" s="7">
+      <c r="D325" s="3">
         <v>210</v>
       </c>
-      <c r="E325" s="7" t="s">
+      <c r="E325" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F325" s="7">
+      <c r="F325" s="3">
         <v>79461.2</v>
       </c>
-      <c r="G325" s="7">
+      <c r="G325" s="3">
         <v>4550</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A326" s="8">
+      <c r="A326" s="2">
         <v>7584401</v>
       </c>
-      <c r="B326" s="8" t="s">
+      <c r="B326" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C326" s="6">
         <v>0</v>
       </c>
-      <c r="D326" s="7">
+      <c r="D326" s="3">
         <v>210</v>
       </c>
-      <c r="E326" s="7" t="s">
+      <c r="E326" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F326" s="7">
+      <c r="F326" s="3">
         <v>60463.19999999999</v>
       </c>
-      <c r="G326" s="7">
+      <c r="G326" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A327" s="8">
+      <c r="A327" s="2">
         <v>2909401</v>
       </c>
-      <c r="B327" s="8" t="s">
+      <c r="B327" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C327" s="6">
         <v>0</v>
       </c>
-      <c r="D327" s="7">
+      <c r="D327" s="3">
         <v>182</v>
       </c>
-      <c r="E327" s="7" t="s">
+      <c r="E327" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F327" s="7">
+      <c r="F327" s="3">
         <v>73348.799999999988</v>
       </c>
-      <c r="G327" s="7">
+      <c r="G327" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A328" s="8">
+      <c r="A328" s="2">
         <v>7742451</v>
       </c>
-      <c r="B328" s="8" t="s">
+      <c r="B328" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C328" s="6">
         <v>0</v>
       </c>
-      <c r="D328" s="7">
+      <c r="D328" s="3">
         <v>26</v>
       </c>
-      <c r="E328" s="7" t="s">
+      <c r="E328" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F328" s="7">
+      <c r="F328" s="3">
         <v>68723.199999999997</v>
       </c>
-      <c r="G328" s="7">
+      <c r="G328" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A329" s="8">
+      <c r="A329" s="2">
         <v>3040288</v>
       </c>
-      <c r="B329" s="8" t="s">
+      <c r="B329" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C329" s="6">
         <v>0</v>
       </c>
-      <c r="D329" s="7">
+      <c r="D329" s="3">
         <v>50</v>
       </c>
-      <c r="E329" s="7" t="s">
+      <c r="E329" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F329" s="7">
+      <c r="F329" s="3">
         <v>5614.44</v>
       </c>
-      <c r="G329" s="7">
+      <c r="G329" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A330" s="8">
+      <c r="A330" s="2">
         <v>3006271</v>
       </c>
-      <c r="B330" s="8" t="s">
+      <c r="B330" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C330" s="6">
         <v>0</v>
       </c>
-      <c r="D330" s="7">
+      <c r="D330" s="3">
         <v>26</v>
       </c>
-      <c r="E330" s="7" t="s">
+      <c r="E330" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F330" s="7">
+      <c r="F330" s="3">
         <v>14632</v>
       </c>
-      <c r="G330" s="7">
+      <c r="G330" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A331" s="8">
+      <c r="A331" s="2">
         <v>3006288</v>
       </c>
-      <c r="B331" s="8" t="s">
+      <c r="B331" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C331" s="6">
         <v>0</v>
       </c>
-      <c r="D331" s="7">
+      <c r="D331" s="3">
         <v>210</v>
       </c>
-      <c r="E331" s="7" t="s">
+      <c r="E331" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F331" s="7">
+      <c r="F331" s="3">
         <v>7639.32</v>
       </c>
-      <c r="G331" s="7">
+      <c r="G331" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A332" s="8">
+      <c r="A332" s="2">
         <v>3001401</v>
       </c>
-      <c r="B332" s="8" t="s">
+      <c r="B332" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C332" s="6">
         <v>0</v>
       </c>
-      <c r="D332" s="7">
+      <c r="D332" s="3">
         <v>210</v>
       </c>
-      <c r="E332" s="7" t="s">
+      <c r="E332" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F332" s="7">
+      <c r="F332" s="3">
         <v>49560</v>
       </c>
-      <c r="G332" s="7">
+      <c r="G332" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A333" s="8">
+      <c r="A333" s="2">
         <v>3002401</v>
       </c>
-      <c r="B333" s="8" t="s">
+      <c r="B333" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C333" s="6">
         <v>0</v>
       </c>
-      <c r="D333" s="7">
+      <c r="D333" s="3">
         <v>210</v>
       </c>
-      <c r="E333" s="7" t="s">
+      <c r="E333" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F333" s="7">
+      <c r="F333" s="3">
         <v>50798.999999999993</v>
       </c>
-      <c r="G333" s="7">
+      <c r="G333" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A334" s="8">
+      <c r="A334" s="2">
         <v>3006401</v>
       </c>
-      <c r="B334" s="8" t="s">
+      <c r="B334" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C334" s="6">
         <v>0</v>
       </c>
-      <c r="D334" s="7">
+      <c r="D334" s="3">
         <v>210</v>
       </c>
-      <c r="E334" s="7" t="s">
+      <c r="E334" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F334" s="7">
+      <c r="F334" s="3">
         <v>53277</v>
       </c>
-      <c r="G334" s="7">
+      <c r="G334" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A335" s="8">
+      <c r="A335" s="2">
         <v>3007403</v>
       </c>
-      <c r="B335" s="8" t="s">
+      <c r="B335" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C335" s="6">
         <v>0</v>
       </c>
-      <c r="D335" s="7">
+      <c r="D335" s="3">
         <v>210</v>
       </c>
-      <c r="E335" s="7" t="s">
+      <c r="E335" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F335" s="7">
+      <c r="F335" s="3">
         <v>61950</v>
       </c>
-      <c r="G335" s="7">
+      <c r="G335" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A336" s="8">
+      <c r="A336" s="2">
         <v>3020401</v>
       </c>
-      <c r="B336" s="8" t="s">
+      <c r="B336" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C336" s="6">
         <v>0</v>
       </c>
-      <c r="D336" s="7">
+      <c r="D336" s="3">
         <v>210</v>
       </c>
-      <c r="E336" s="7" t="s">
+      <c r="E336" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F336" s="7">
+      <c r="F336" s="3">
         <v>58976.399999999994</v>
       </c>
-      <c r="G336" s="7">
+      <c r="G336" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A337" s="8">
+      <c r="A337" s="2">
         <v>3017401</v>
       </c>
-      <c r="B337" s="8" t="s">
+      <c r="B337" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C337" s="6">
         <v>0</v>
       </c>
-      <c r="D337" s="7">
+      <c r="D337" s="3">
         <v>210</v>
       </c>
-      <c r="E337" s="7" t="s">
+      <c r="E337" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F337" s="7">
+      <c r="F337" s="3">
         <v>61206.6</v>
       </c>
-      <c r="G337" s="7">
+      <c r="G337" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A338" s="8">
+      <c r="A338" s="2">
         <v>3019401</v>
       </c>
-      <c r="B338" s="8" t="s">
+      <c r="B338" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C338" s="6">
         <v>0</v>
       </c>
-      <c r="D338" s="7">
+      <c r="D338" s="3">
         <v>210</v>
       </c>
-      <c r="E338" s="7" t="s">
+      <c r="E338" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F338" s="7">
+      <c r="F338" s="3">
         <v>57241.799999999996</v>
       </c>
-      <c r="G338" s="7">
+      <c r="G338" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A339" s="8">
+      <c r="A339" s="2">
         <v>3064401</v>
       </c>
-      <c r="B339" s="8" t="s">
+      <c r="B339" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C339" s="6">
         <v>0</v>
       </c>
-      <c r="D339" s="7">
+      <c r="D339" s="3">
         <v>210</v>
       </c>
-      <c r="E339" s="7" t="s">
+      <c r="E339" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F339" s="7">
+      <c r="F339" s="3">
         <v>56250.600000000006</v>
       </c>
-      <c r="G339" s="7">
+      <c r="G339" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A340" s="8">
+      <c r="A340" s="2">
         <v>3081401</v>
       </c>
-      <c r="B340" s="8" t="s">
+      <c r="B340" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C340" s="6">
         <v>0</v>
       </c>
-      <c r="D340" s="7">
+      <c r="D340" s="3">
         <v>210</v>
       </c>
-      <c r="E340" s="7" t="s">
+      <c r="E340" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F340" s="7">
+      <c r="F340" s="3">
         <v>58480.799999999988</v>
       </c>
-      <c r="G340" s="7">
+      <c r="G340" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A341" s="8">
+      <c r="A341" s="2">
         <v>3082401</v>
       </c>
-      <c r="B341" s="8" t="s">
+      <c r="B341" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C341" s="6">
         <v>0</v>
       </c>
-      <c r="D341" s="7">
+      <c r="D341" s="3">
         <v>210</v>
       </c>
-      <c r="E341" s="7" t="s">
+      <c r="E341" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F341" s="7">
+      <c r="F341" s="3">
         <v>59719.799999999996</v>
       </c>
-      <c r="G341" s="7">
+      <c r="G341" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A342" s="8">
+      <c r="A342" s="2">
         <v>3084401</v>
       </c>
-      <c r="B342" s="8" t="s">
+      <c r="B342" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C342" s="6">
         <v>0</v>
       </c>
-      <c r="D342" s="7">
+      <c r="D342" s="3">
         <v>210</v>
       </c>
-      <c r="E342" s="7" t="s">
+      <c r="E342" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F342" s="7">
+      <c r="F342" s="3">
         <v>62197.8</v>
       </c>
-      <c r="G342" s="7">
+      <c r="G342" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A343" s="8">
+      <c r="A343" s="2">
         <v>3121401</v>
       </c>
-      <c r="B343" s="8" t="s">
+      <c r="B343" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C343" s="6">
         <v>0</v>
       </c>
-      <c r="D343" s="7">
+      <c r="D343" s="3">
         <v>210</v>
       </c>
-      <c r="E343" s="7" t="s">
+      <c r="E343" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F343" s="7">
+      <c r="F343" s="3">
         <v>59472</v>
       </c>
-      <c r="G343" s="7">
+      <c r="G343" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A344" s="8">
+      <c r="A344" s="2">
         <v>3122401</v>
       </c>
-      <c r="B344" s="8" t="s">
+      <c r="B344" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C344" s="6">
         <v>0</v>
       </c>
-      <c r="D344" s="7">
+      <c r="D344" s="3">
         <v>210</v>
       </c>
-      <c r="E344" s="7" t="s">
+      <c r="E344" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F344" s="7">
+      <c r="F344" s="3">
         <v>60710.999999999993</v>
       </c>
-      <c r="G344" s="7">
+      <c r="G344" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A345" s="8">
+      <c r="A345" s="2">
         <v>3614401</v>
       </c>
-      <c r="B345" s="8" t="s">
+      <c r="B345" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C345" s="6">
         <v>0</v>
       </c>
-      <c r="D345" s="7">
+      <c r="D345" s="3">
         <v>210</v>
       </c>
-      <c r="E345" s="7" t="s">
+      <c r="E345" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F345" s="7">
+      <c r="F345" s="3">
         <v>63684.6</v>
       </c>
-      <c r="G345" s="7">
+      <c r="G345" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A346" s="8">
+      <c r="A346" s="2">
         <v>3617401</v>
       </c>
-      <c r="B346" s="8" t="s">
+      <c r="B346" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C346" s="6">
         <v>0</v>
       </c>
-      <c r="D346" s="7">
+      <c r="D346" s="3">
         <v>210</v>
       </c>
-      <c r="E346" s="7" t="s">
+      <c r="E346" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F346" s="7">
+      <c r="F346" s="3">
         <v>61702.2</v>
       </c>
-      <c r="G346" s="7">
+      <c r="G346" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A347" s="8">
+      <c r="A347" s="2">
         <v>3923401</v>
       </c>
-      <c r="B347" s="8" t="s">
+      <c r="B347" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C347" s="6">
         <v>0</v>
       </c>
-      <c r="D347" s="7">
+      <c r="D347" s="3">
         <v>210</v>
       </c>
-      <c r="E347" s="7" t="s">
+      <c r="E347" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F347" s="7">
+      <c r="F347" s="3">
         <v>52285.799999999996</v>
       </c>
-      <c r="G347" s="7">
+      <c r="G347" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A348" s="8">
+      <c r="A348" s="2">
         <v>4803401</v>
       </c>
-      <c r="B348" s="8" t="s">
+      <c r="B348" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C348" s="6">
         <v>0</v>
       </c>
-      <c r="D348" s="7">
+      <c r="D348" s="3">
         <v>210</v>
       </c>
-      <c r="E348" s="7" t="s">
+      <c r="E348" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F348" s="7">
+      <c r="F348" s="3">
         <v>53772.6</v>
       </c>
-      <c r="G348" s="7">
+      <c r="G348" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A349" s="8">
+      <c r="A349" s="2">
         <v>4811401</v>
       </c>
-      <c r="B349" s="8" t="s">
+      <c r="B349" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C349" s="6">
         <v>0</v>
       </c>
-      <c r="D349" s="7">
+      <c r="D349" s="3">
         <v>210</v>
       </c>
-      <c r="E349" s="7" t="s">
+      <c r="E349" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F349" s="7">
+      <c r="F349" s="3">
         <v>56993.999999999993</v>
       </c>
-      <c r="G349" s="7">
+      <c r="G349" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A350" s="8">
+      <c r="A350" s="2">
         <v>4501401</v>
       </c>
-      <c r="B350" s="8" t="s">
+      <c r="B350" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C350" s="6">
         <v>0</v>
       </c>
-      <c r="D350" s="7">
+      <c r="D350" s="3">
         <v>210</v>
       </c>
-      <c r="E350" s="7" t="s">
+      <c r="E350" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F350" s="7">
+      <c r="F350" s="3">
         <v>56993.999999999993</v>
       </c>
-      <c r="G350" s="7">
+      <c r="G350" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A351" s="8">
+      <c r="A351" s="2">
         <v>7403401</v>
       </c>
-      <c r="B351" s="8" t="s">
+      <c r="B351" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C351" s="6">
         <v>0</v>
       </c>
-      <c r="D351" s="7">
+      <c r="D351" s="3">
         <v>210</v>
       </c>
-      <c r="E351" s="7" t="s">
+      <c r="E351" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F351" s="7">
+      <c r="F351" s="3">
         <v>39648</v>
       </c>
-      <c r="G351" s="7">
+      <c r="G351" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A352" s="8">
+      <c r="A352" s="2">
         <v>7330403</v>
       </c>
-      <c r="B352" s="8" t="s">
+      <c r="B352" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C352" s="6">
         <v>0</v>
       </c>
-      <c r="D352" s="7">
+      <c r="D352" s="3">
         <v>210</v>
       </c>
-      <c r="E352" s="7" t="s">
+      <c r="E352" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F352" s="7">
+      <c r="F352" s="3">
         <v>17098.2</v>
       </c>
-      <c r="G352" s="7">
+      <c r="G352" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A353" s="2">
+        <v>7079401</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C353" s="6">
+        <v>0</v>
+      </c>
+      <c r="D353" s="3">
+        <v>210</v>
+      </c>
+      <c r="E353" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F353" s="3">
+        <v>85890</v>
+      </c>
+      <c r="G353" s="3">
         <v>0</v>
       </c>
     </row>
